--- a/Employee_Wellness_Scoring_System.xlsx
+++ b/Employee_Wellness_Scoring_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adityabirla-my.sharepoint.com/personal/rajan_anilgupta_adityabirla_com/Documents/Desktop/Techie/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="11_AB1E656E9F47FBFC57958C43F61CEE78F1214856" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66FB36D9-98E7-4067-907F-F6AA784829BB}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="11_AB1E656E9F47FBFC57958C43F61CEE78F1214856" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B15F33C-CACA-48A8-85E1-4A7ABD4BCFE5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="641" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="641" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee_Master" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Leaderboard!$A$1:$D$182</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Participation_Entry!$A$1:$L$542</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -1190,7 +1191,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -16393,7 +16401,7 @@
     <sortCondition ref="B2:B172"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39115,22 +39123,22 @@
     <protectedRange sqref="B302" name="Range1_2_2"/>
   </protectedRanges>
   <conditionalFormatting sqref="B2:B92">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:B16 B2">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:B101">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -39156,7 +39164,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D182"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
@@ -39182,11 +39190,11 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="6">
-        <v>416087</v>
+        <v>450230</v>
       </c>
       <c r="B2" s="7" t="str">
         <f>IFERROR(VLOOKUP(A2,Employee_Master!A:B,2,0),"")</f>
-        <v>Manoj Singh</v>
+        <v>Aarti Gupta</v>
       </c>
       <c r="C2" s="7" t="str">
         <f>IFERROR(VLOOKUP(A2,Employee_Master!A:B,3,0),"")</f>
@@ -39194,16 +39202,16 @@
       </c>
       <c r="D2" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A2,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A2,Participation_Entry!L:L))</f>
-        <v>20</v>
+        <v>72.238799999999998</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="6">
-        <v>365114</v>
+        <v>452073</v>
       </c>
       <c r="B3" s="7" t="str">
         <f>IFERROR(VLOOKUP(A3,Employee_Master!A:B,2,0),"")</f>
-        <v>Bhanu Sirohi</v>
+        <v xml:space="preserve">Aashish </v>
       </c>
       <c r="C3" s="7" t="str">
         <f>IFERROR(VLOOKUP(A3,Employee_Master!A:B,3,0),"")</f>
@@ -39211,16 +39219,16 @@
       </c>
       <c r="D3" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A3,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A3,Participation_Entry!L:L))</f>
-        <v>170.11259999999999</v>
+        <v>63.355499999999999</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6">
-        <v>460812</v>
+        <v>461161</v>
       </c>
       <c r="B4" s="7" t="str">
         <f>IFERROR(VLOOKUP(A4,Employee_Master!A:B,2,0),"")</f>
-        <v>Deepak Sharma</v>
+        <v>Abhay Singh</v>
       </c>
       <c r="C4" s="7" t="str">
         <f>IFERROR(VLOOKUP(A4,Employee_Master!A:B,3,0),"")</f>
@@ -39228,16 +39236,16 @@
       </c>
       <c r="D4" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A4,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A4,Participation_Entry!L:L))</f>
-        <v>67.504199999999997</v>
+        <v>42.836399999999998</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6">
-        <v>473266</v>
+        <v>456091</v>
       </c>
       <c r="B5" s="7" t="str">
         <f>IFERROR(VLOOKUP(A5,Employee_Master!A:B,2,0),"")</f>
-        <v>Jitender Yadav</v>
+        <v>Abhinesh Pandey</v>
       </c>
       <c r="C5" s="7" t="str">
         <f>IFERROR(VLOOKUP(A5,Employee_Master!A:B,3,0),"")</f>
@@ -39245,16 +39253,16 @@
       </c>
       <c r="D5" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A5,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A5,Participation_Entry!L:L))</f>
-        <v>45.494999999999997</v>
+        <v>55.546899999999994</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6">
-        <v>420533</v>
+        <v>478308</v>
       </c>
       <c r="B6" s="7" t="str">
         <f>IFERROR(VLOOKUP(A6,Employee_Master!A:B,2,0),"")</f>
-        <v>Gaurav Saxena</v>
+        <v xml:space="preserve">Abhishek savita </v>
       </c>
       <c r="C6" s="7" t="str">
         <f>IFERROR(VLOOKUP(A6,Employee_Master!A:B,3,0),"")</f>
@@ -39262,33 +39270,33 @@
       </c>
       <c r="D6" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A6,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A6,Participation_Entry!L:L))</f>
-        <v>30</v>
+        <v>88.970200000000006</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6">
-        <v>465181</v>
+        <v>478266</v>
       </c>
       <c r="B7" s="7" t="str">
         <f>IFERROR(VLOOKUP(A7,Employee_Master!A:B,2,0),"")</f>
-        <v>Gaurav Singh Gurjar</v>
+        <v xml:space="preserve">Abhishek Sharma </v>
       </c>
       <c r="C7" s="7" t="str">
         <f>IFERROR(VLOOKUP(A7,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D7" s="7" t="str">
+      <c r="D7" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A7,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A7,Participation_Entry!L:L))</f>
-        <v/>
+        <v>35.4343</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6">
-        <v>434518</v>
+        <v>466167</v>
       </c>
       <c r="B8" s="7" t="str">
         <f>IFERROR(VLOOKUP(A8,Employee_Master!A:B,2,0),"")</f>
-        <v>Maneesh Mohan</v>
+        <v>Aishwarya Sharma</v>
       </c>
       <c r="C8" s="7" t="str">
         <f>IFERROR(VLOOKUP(A8,Employee_Master!A:B,3,0),"")</f>
@@ -39296,16 +39304,16 @@
       </c>
       <c r="D8" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A8,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A8,Participation_Entry!L:L))</f>
-        <v>82.684799999999996</v>
+        <v>151.4357</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6">
-        <v>463660</v>
+        <v>712428</v>
       </c>
       <c r="B9" s="7" t="str">
         <f>IFERROR(VLOOKUP(A9,Employee_Master!A:B,2,0),"")</f>
-        <v>Rohit Sharma</v>
+        <v>Akanksha Gangwar</v>
       </c>
       <c r="C9" s="7" t="str">
         <f>IFERROR(VLOOKUP(A9,Employee_Master!A:B,3,0),"")</f>
@@ -39313,16 +39321,16 @@
       </c>
       <c r="D9" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A9,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A9,Participation_Entry!L:L))</f>
-        <v>26.242999999999999</v>
+        <v>73.302199999999999</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6">
-        <v>484877</v>
+        <v>454456</v>
       </c>
       <c r="B10" s="7" t="str">
         <f>IFERROR(VLOOKUP(A10,Employee_Master!A:B,2,0),"")</f>
-        <v>Prashant Gupta</v>
+        <v>Akash Deshmukh</v>
       </c>
       <c r="C10" s="7" t="str">
         <f>IFERROR(VLOOKUP(A10,Employee_Master!A:B,3,0),"")</f>
@@ -39330,50 +39338,50 @@
       </c>
       <c r="D10" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A10,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A10,Participation_Entry!L:L))</f>
-        <v>47.981999999999999</v>
+        <v>118.25749999999999</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6">
-        <v>411573</v>
+        <v>452119</v>
       </c>
       <c r="B11" s="7" t="str">
         <f>IFERROR(VLOOKUP(A11,Employee_Master!A:B,2,0),"")</f>
-        <v>Atishay Dwivedi</v>
+        <v>Akhil Tiwari</v>
       </c>
       <c r="C11" s="7" t="str">
         <f>IFERROR(VLOOKUP(A11,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D11" s="7" t="str">
+      <c r="D11" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A11,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A11,Participation_Entry!L:L))</f>
-        <v/>
+        <v>80.690899999999999</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="6">
-        <v>410040</v>
+        <v>430977</v>
       </c>
       <c r="B12" s="7" t="str">
         <f>IFERROR(VLOOKUP(A12,Employee_Master!A:B,2,0),"")</f>
-        <v>Deepak Singh</v>
+        <v>Akshit Sood</v>
       </c>
       <c r="C12" s="7" t="str">
         <f>IFERROR(VLOOKUP(A12,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D12" s="7" t="str">
+      <c r="D12" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A12,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A12,Participation_Entry!L:L))</f>
-        <v/>
+        <v>69.620400000000004</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6">
-        <v>433939</v>
+        <v>451857</v>
       </c>
       <c r="B13" s="7" t="str">
         <f>IFERROR(VLOOKUP(A13,Employee_Master!A:B,2,0),"")</f>
-        <v>Manish Kumar</v>
+        <v xml:space="preserve">Amar Kumar </v>
       </c>
       <c r="C13" s="7" t="str">
         <f>IFERROR(VLOOKUP(A13,Employee_Master!A:B,3,0),"")</f>
@@ -39381,16 +39389,16 @@
       </c>
       <c r="D13" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A13,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A13,Participation_Entry!L:L))</f>
-        <v>47.6008</v>
+        <v>64.830199999999991</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6">
-        <v>451567</v>
+        <v>427568</v>
       </c>
       <c r="B14" s="7" t="str">
         <f>IFERROR(VLOOKUP(A14,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Gaurav Kumar  </v>
+        <v>Anjali Sundrani</v>
       </c>
       <c r="C14" s="7" t="str">
         <f>IFERROR(VLOOKUP(A14,Employee_Master!A:B,3,0),"")</f>
@@ -39398,16 +39406,16 @@
       </c>
       <c r="D14" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A14,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A14,Participation_Entry!L:L))</f>
-        <v>40</v>
+        <v>18.665300000000002</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6">
-        <v>408627</v>
+        <v>469899</v>
       </c>
       <c r="B15" s="7" t="str">
         <f>IFERROR(VLOOKUP(A15,Employee_Master!A:B,2,0),"")</f>
-        <v>Govind Rai</v>
+        <v>Ankit</v>
       </c>
       <c r="C15" s="7" t="str">
         <f>IFERROR(VLOOKUP(A15,Employee_Master!A:B,3,0),"")</f>
@@ -39415,33 +39423,33 @@
       </c>
       <c r="D15" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A15,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A15,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6">
-        <v>407302</v>
+        <v>451858</v>
       </c>
       <c r="B16" s="7" t="str">
         <f>IFERROR(VLOOKUP(A16,Employee_Master!A:B,2,0),"")</f>
-        <v>Sanjaya Sahoo</v>
+        <v>Ankit Bhardwaj</v>
       </c>
       <c r="C16" s="7" t="str">
         <f>IFERROR(VLOOKUP(A16,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D16" s="7" t="str">
+      <c r="D16" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A16,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A16,Participation_Entry!L:L))</f>
-        <v/>
+        <v>34.916600000000003</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6">
-        <v>427568</v>
+        <v>486309</v>
       </c>
       <c r="B17" s="7" t="str">
         <f>IFERROR(VLOOKUP(A17,Employee_Master!A:B,2,0),"")</f>
-        <v>Anjali Sundrani</v>
+        <v>Ankit Bhatt</v>
       </c>
       <c r="C17" s="7" t="str">
         <f>IFERROR(VLOOKUP(A17,Employee_Master!A:B,3,0),"")</f>
@@ -39449,33 +39457,33 @@
       </c>
       <c r="D17" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A17,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A17,Participation_Entry!L:L))</f>
-        <v>18.665300000000002</v>
+        <v>86.121200000000002</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6">
-        <v>447096</v>
+        <v>470301</v>
       </c>
       <c r="B18" s="7" t="str">
         <f>IFERROR(VLOOKUP(A18,Employee_Master!A:B,2,0),"")</f>
-        <v>Deepak Tiwari</v>
+        <v>Ankit Kumar</v>
       </c>
       <c r="C18" s="7" t="str">
         <f>IFERROR(VLOOKUP(A18,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D18" s="7" t="str">
+      <c r="D18" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A18,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A18,Participation_Entry!L:L))</f>
-        <v/>
+        <v>76.212099999999992</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="6">
-        <v>408262</v>
+        <v>468157</v>
       </c>
       <c r="B19" s="7" t="str">
         <f>IFERROR(VLOOKUP(A19,Employee_Master!A:B,2,0),"")</f>
-        <v>Arpanjot Singh</v>
+        <v>Ankit Tiwari</v>
       </c>
       <c r="C19" s="7" t="str">
         <f>IFERROR(VLOOKUP(A19,Employee_Master!A:B,3,0),"")</f>
@@ -39483,16 +39491,16 @@
       </c>
       <c r="D19" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A19,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A19,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>48.702200000000005</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="6">
-        <v>451509</v>
+        <v>452115</v>
       </c>
       <c r="B20" s="7" t="str">
         <f>IFERROR(VLOOKUP(A20,Employee_Master!A:B,2,0),"")</f>
-        <v>Vivek Aswal</v>
+        <v xml:space="preserve">Anshul Sharma </v>
       </c>
       <c r="C20" s="7" t="str">
         <f>IFERROR(VLOOKUP(A20,Employee_Master!A:B,3,0),"")</f>
@@ -39500,16 +39508,16 @@
       </c>
       <c r="D20" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A20,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A20,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="6">
-        <v>460284</v>
+        <v>467068</v>
       </c>
       <c r="B21" s="7" t="str">
         <f>IFERROR(VLOOKUP(A21,Employee_Master!A:B,2,0),"")</f>
-        <v>Madhu Aggu</v>
+        <v>Anuj Kumar</v>
       </c>
       <c r="C21" s="7" t="str">
         <f>IFERROR(VLOOKUP(A21,Employee_Master!A:B,3,0),"")</f>
@@ -39517,16 +39525,16 @@
       </c>
       <c r="D21" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A21,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A21,Participation_Entry!L:L))</f>
-        <v>62.599800000000002</v>
+        <v>79.665700000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="6">
-        <v>464188</v>
+        <v>466367</v>
       </c>
       <c r="B22" s="7" t="str">
         <f>IFERROR(VLOOKUP(A22,Employee_Master!A:B,2,0),"")</f>
-        <v>Himanshu Saini</v>
+        <v>Arjun Sharma</v>
       </c>
       <c r="C22" s="7" t="str">
         <f>IFERROR(VLOOKUP(A22,Employee_Master!A:B,3,0),"")</f>
@@ -39534,33 +39542,33 @@
       </c>
       <c r="D22" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A22,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A22,Participation_Entry!L:L))</f>
-        <v>105.45070000000001</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="6">
-        <v>470292</v>
+        <v>492857</v>
       </c>
       <c r="B23" s="7" t="str">
         <f>IFERROR(VLOOKUP(A23,Employee_Master!A:B,2,0),"")</f>
-        <v>Vishal Kumar</v>
+        <v>Arnima Thakur</v>
       </c>
       <c r="C23" s="7" t="str">
         <f>IFERROR(VLOOKUP(A23,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D23" s="7" t="str">
+      <c r="D23" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A23,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A23,Participation_Entry!L:L))</f>
-        <v/>
+        <v>47.4846</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="6">
-        <v>438263</v>
+        <v>408262</v>
       </c>
       <c r="B24" s="7" t="str">
         <f>IFERROR(VLOOKUP(A24,Employee_Master!A:B,2,0),"")</f>
-        <v>Vikash Kumar</v>
+        <v>Arpanjot Singh</v>
       </c>
       <c r="C24" s="7" t="str">
         <f>IFERROR(VLOOKUP(A24,Employee_Master!A:B,3,0),"")</f>
@@ -39568,16 +39576,16 @@
       </c>
       <c r="D24" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A24,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A24,Participation_Entry!L:L))</f>
-        <v>63.443200000000004</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="6">
-        <v>456743</v>
+        <v>453089</v>
       </c>
       <c r="B25" s="7" t="str">
         <f>IFERROR(VLOOKUP(A25,Employee_Master!A:B,2,0),"")</f>
-        <v>Chironjee Narvare</v>
+        <v>Arun Lamba</v>
       </c>
       <c r="C25" s="7" t="str">
         <f>IFERROR(VLOOKUP(A25,Employee_Master!A:B,3,0),"")</f>
@@ -39585,16 +39593,16 @@
       </c>
       <c r="D25" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A25,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A25,Participation_Entry!L:L))</f>
-        <v>32.647199999999998</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="6">
-        <v>420109</v>
+        <v>449890</v>
       </c>
       <c r="B26" s="7" t="str">
         <f>IFERROR(VLOOKUP(A26,Employee_Master!A:B,2,0),"")</f>
-        <v>Chandraprakash Nandwana</v>
+        <v xml:space="preserve">Ashish Baghel </v>
       </c>
       <c r="C26" s="7" t="str">
         <f>IFERROR(VLOOKUP(A26,Employee_Master!A:B,3,0),"")</f>
@@ -39602,16 +39610,16 @@
       </c>
       <c r="D26" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A26,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A26,Participation_Entry!L:L))</f>
-        <v>81.180800000000005</v>
+        <v>50.825800000000001</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="6">
-        <v>479827</v>
+        <v>453948</v>
       </c>
       <c r="B27" s="7" t="str">
         <f>IFERROR(VLOOKUP(A27,Employee_Master!A:B,2,0),"")</f>
-        <v>Sunil Kr. Singh</v>
+        <v>Ashish Bhardwaj</v>
       </c>
       <c r="C27" s="7" t="str">
         <f>IFERROR(VLOOKUP(A27,Employee_Master!A:B,3,0),"")</f>
@@ -39619,16 +39627,16 @@
       </c>
       <c r="D27" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A27,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A27,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>68.705600000000004</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="6">
-        <v>488518</v>
+        <v>478084</v>
       </c>
       <c r="B28" s="7" t="str">
         <f>IFERROR(VLOOKUP(A28,Employee_Master!A:B,2,0),"")</f>
-        <v>Neha Chaturvedi</v>
+        <v>Ashish Mishra</v>
       </c>
       <c r="C28" s="7" t="str">
         <f>IFERROR(VLOOKUP(A28,Employee_Master!A:B,3,0),"")</f>
@@ -39636,16 +39644,16 @@
       </c>
       <c r="D28" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A28,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A28,Participation_Entry!L:L))</f>
-        <v>33.218600000000002</v>
+        <v>102.2955</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="6">
-        <v>437534</v>
+        <v>722356</v>
       </c>
       <c r="B29" s="7" t="str">
         <f>IFERROR(VLOOKUP(A29,Employee_Master!A:B,2,0),"")</f>
-        <v>Himanshu Sangar</v>
+        <v>Ashita Munjley</v>
       </c>
       <c r="C29" s="7" t="str">
         <f>IFERROR(VLOOKUP(A29,Employee_Master!A:B,3,0),"")</f>
@@ -39653,50 +39661,50 @@
       </c>
       <c r="D29" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A29,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A29,Participation_Entry!L:L))</f>
-        <v>176.45569999999998</v>
+        <v>34.984099999999998</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="6">
-        <v>464500</v>
+        <v>411573</v>
       </c>
       <c r="B30" s="7" t="str">
         <f>IFERROR(VLOOKUP(A30,Employee_Master!A:B,2,0),"")</f>
-        <v>Dalip Sharma</v>
+        <v>Atishay Dwivedi</v>
       </c>
       <c r="C30" s="7" t="str">
         <f>IFERROR(VLOOKUP(A30,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A30,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A30,Participation_Entry!L:L))</f>
-        <v>79.0274</v>
+        <v/>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="6">
-        <v>492857</v>
+        <v>468456</v>
       </c>
       <c r="B31" s="7" t="str">
         <f>IFERROR(VLOOKUP(A31,Employee_Master!A:B,2,0),"")</f>
-        <v>Arnima Thakur</v>
+        <v>Ayush Joshi</v>
       </c>
       <c r="C31" s="7" t="str">
         <f>IFERROR(VLOOKUP(A31,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A31,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A31,Participation_Entry!L:L))</f>
-        <v>47.4846</v>
+        <v/>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="6">
-        <v>412273</v>
+      <c r="A32" s="15">
+        <v>466445</v>
       </c>
       <c r="B32" s="7" t="str">
         <f>IFERROR(VLOOKUP(A32,Employee_Master!A:B,2,0),"")</f>
-        <v>Sandeep Sengar</v>
+        <v>Ayush Kumar</v>
       </c>
       <c r="C32" s="7" t="str">
         <f>IFERROR(VLOOKUP(A32,Employee_Master!A:B,3,0),"")</f>
@@ -39704,16 +39712,16 @@
       </c>
       <c r="D32" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A32,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A32,Participation_Entry!L:L))</f>
-        <v>21.326900000000002</v>
+        <v>65.553899999999999</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="6">
-        <v>451609</v>
+      <c r="A33" s="15">
+        <v>365114</v>
       </c>
       <c r="B33" s="7" t="str">
         <f>IFERROR(VLOOKUP(A33,Employee_Master!A:B,2,0),"")</f>
-        <v>Vivek Kumar Yadav</v>
+        <v>Bhanu Sirohi</v>
       </c>
       <c r="C33" s="7" t="str">
         <f>IFERROR(VLOOKUP(A33,Employee_Master!A:B,3,0),"")</f>
@@ -39721,16 +39729,16 @@
       </c>
       <c r="D33" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A33,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A33,Participation_Entry!L:L))</f>
-        <v>92.552499999999995</v>
+        <v>170.11259999999999</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="6">
-        <v>424332</v>
+        <v>452058</v>
       </c>
       <c r="B34" s="7" t="str">
         <f>IFERROR(VLOOKUP(A34,Employee_Master!A:B,2,0),"")</f>
-        <v>Naresh Kumar</v>
+        <v>Bhavya Gupta</v>
       </c>
       <c r="C34" s="7" t="str">
         <f>IFERROR(VLOOKUP(A34,Employee_Master!A:B,3,0),"")</f>
@@ -39738,16 +39746,16 @@
       </c>
       <c r="D34" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A34,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A34,Participation_Entry!L:L))</f>
-        <v>86.822200000000009</v>
+        <v>70.827600000000004</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="6">
-        <v>456091</v>
+        <v>721766</v>
       </c>
       <c r="B35" s="7" t="str">
         <f>IFERROR(VLOOKUP(A35,Employee_Master!A:B,2,0),"")</f>
-        <v>Abhinesh Pandey</v>
+        <v>BHAWNA SHARMA</v>
       </c>
       <c r="C35" s="7" t="str">
         <f>IFERROR(VLOOKUP(A35,Employee_Master!A:B,3,0),"")</f>
@@ -39755,16 +39763,16 @@
       </c>
       <c r="D35" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A35,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A35,Participation_Entry!L:L))</f>
-        <v>55.546899999999994</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="6">
-        <v>445891</v>
+      <c r="A36" s="15">
+        <v>420109</v>
       </c>
       <c r="B36" s="7" t="str">
         <f>IFERROR(VLOOKUP(A36,Employee_Master!A:B,2,0),"")</f>
-        <v>Parmvir Singh</v>
+        <v>Chandraprakash Nandwana</v>
       </c>
       <c r="C36" s="7" t="str">
         <f>IFERROR(VLOOKUP(A36,Employee_Master!A:B,3,0),"")</f>
@@ -39772,16 +39780,16 @@
       </c>
       <c r="D36" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A36,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A36,Participation_Entry!L:L))</f>
-        <v>32.670700000000004</v>
+        <v>81.180800000000005</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6">
-        <v>467519</v>
+        <v>456743</v>
       </c>
       <c r="B37" s="7" t="str">
         <f>IFERROR(VLOOKUP(A37,Employee_Master!A:B,2,0),"")</f>
-        <v>Vivek Tiwari</v>
+        <v>Chironjee Narvare</v>
       </c>
       <c r="C37" s="7" t="str">
         <f>IFERROR(VLOOKUP(A37,Employee_Master!A:B,3,0),"")</f>
@@ -39789,16 +39797,16 @@
       </c>
       <c r="D37" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A37,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A37,Participation_Entry!L:L))</f>
-        <v>62.805900000000001</v>
+        <v>32.647199999999998</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6">
-        <v>416828</v>
+        <v>464500</v>
       </c>
       <c r="B38" s="7" t="str">
         <f>IFERROR(VLOOKUP(A38,Employee_Master!A:B,2,0),"")</f>
-        <v>Keshav Dev</v>
+        <v>Dalip Sharma</v>
       </c>
       <c r="C38" s="7" t="str">
         <f>IFERROR(VLOOKUP(A38,Employee_Master!A:B,3,0),"")</f>
@@ -39806,16 +39814,16 @@
       </c>
       <c r="D38" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A38,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A38,Participation_Entry!L:L))</f>
-        <v>110.72030000000001</v>
+        <v>79.0274</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6">
-        <v>430977</v>
+        <v>456706</v>
       </c>
       <c r="B39" s="7" t="str">
         <f>IFERROR(VLOOKUP(A39,Employee_Master!A:B,2,0),"")</f>
-        <v>Akshit Sood</v>
+        <v>Daljit Singh</v>
       </c>
       <c r="C39" s="7" t="str">
         <f>IFERROR(VLOOKUP(A39,Employee_Master!A:B,3,0),"")</f>
@@ -39823,16 +39831,16 @@
       </c>
       <c r="D39" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A39,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A39,Participation_Entry!L:L))</f>
-        <v>69.620400000000004</v>
+        <v>12.424099999999999</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="6">
-        <v>436468</v>
+      <c r="A40" s="15">
+        <v>460812</v>
       </c>
       <c r="B40" s="7" t="str">
         <f>IFERROR(VLOOKUP(A40,Employee_Master!A:B,2,0),"")</f>
-        <v>Karan Singh</v>
+        <v>Deepak Sharma</v>
       </c>
       <c r="C40" s="7" t="str">
         <f>IFERROR(VLOOKUP(A40,Employee_Master!A:B,3,0),"")</f>
@@ -39840,50 +39848,50 @@
       </c>
       <c r="D40" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A40,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A40,Participation_Entry!L:L))</f>
-        <v>20</v>
+        <v>67.504199999999997</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6">
-        <v>438957</v>
+        <v>410040</v>
       </c>
       <c r="B41" s="7" t="str">
         <f>IFERROR(VLOOKUP(A41,Employee_Master!A:B,2,0),"")</f>
-        <v>Risha Bansal</v>
+        <v>Deepak Singh</v>
       </c>
       <c r="C41" s="7" t="str">
         <f>IFERROR(VLOOKUP(A41,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A41,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A41,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v/>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="6">
-        <v>428544</v>
+        <v>447096</v>
       </c>
       <c r="B42" s="7" t="str">
         <f>IFERROR(VLOOKUP(A42,Employee_Master!A:B,2,0),"")</f>
-        <v>Harjot Singh</v>
+        <v>Deepak Tiwari</v>
       </c>
       <c r="C42" s="7" t="str">
         <f>IFERROR(VLOOKUP(A42,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A42,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A42,Participation_Entry!L:L))</f>
-        <v>55.920200000000001</v>
+        <v/>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="6">
-        <v>487107</v>
+        <v>455024</v>
       </c>
       <c r="B43" s="7" t="str">
         <f>IFERROR(VLOOKUP(A43,Employee_Master!A:B,2,0),"")</f>
-        <v>Manish Kr. Singh</v>
+        <v>Dileep Kumar</v>
       </c>
       <c r="C43" s="7" t="str">
         <f>IFERROR(VLOOKUP(A43,Employee_Master!A:B,3,0),"")</f>
@@ -39891,16 +39899,16 @@
       </c>
       <c r="D43" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A43,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A43,Participation_Entry!L:L))</f>
-        <v>53.0854</v>
+        <v>31.736699999999999</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6">
-        <v>423859</v>
+        <v>460513</v>
       </c>
       <c r="B44" s="7" t="str">
         <f>IFERROR(VLOOKUP(A44,Employee_Master!A:B,2,0),"")</f>
-        <v>Tilak Raj</v>
+        <v>Dinesh Kumar</v>
       </c>
       <c r="C44" s="7" t="str">
         <f>IFERROR(VLOOKUP(A44,Employee_Master!A:B,3,0),"")</f>
@@ -39908,16 +39916,16 @@
       </c>
       <c r="D44" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A44,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A44,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>60.249700000000004</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="6">
-        <v>438679</v>
+        <v>451567</v>
       </c>
       <c r="B45" s="7" t="str">
         <f>IFERROR(VLOOKUP(A45,Employee_Master!A:B,2,0),"")</f>
-        <v>Saurabh Kumar</v>
+        <v xml:space="preserve">Gaurav Kumar  </v>
       </c>
       <c r="C45" s="7" t="str">
         <f>IFERROR(VLOOKUP(A45,Employee_Master!A:B,3,0),"")</f>
@@ -39925,16 +39933,16 @@
       </c>
       <c r="D45" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A45,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A45,Participation_Entry!L:L))</f>
-        <v>75.917199999999994</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="6">
-        <v>448882</v>
+        <v>420533</v>
       </c>
       <c r="B46" s="7" t="str">
         <f>IFERROR(VLOOKUP(A46,Employee_Master!A:B,2,0),"")</f>
-        <v>Gurwinder Singh</v>
+        <v>Gaurav Saxena</v>
       </c>
       <c r="C46" s="7" t="str">
         <f>IFERROR(VLOOKUP(A46,Employee_Master!A:B,3,0),"")</f>
@@ -39942,33 +39950,33 @@
       </c>
       <c r="D46" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A46,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A46,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="6">
-        <v>453949</v>
+        <v>465181</v>
       </c>
       <c r="B47" s="7" t="str">
         <f>IFERROR(VLOOKUP(A47,Employee_Master!A:B,2,0),"")</f>
-        <v>Naveen Kumar</v>
+        <v>Gaurav Singh Gurjar</v>
       </c>
       <c r="C47" s="7" t="str">
         <f>IFERROR(VLOOKUP(A47,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A47,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A47,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v/>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="6">
-        <v>440317</v>
+        <v>452991</v>
       </c>
       <c r="B48" s="7" t="str">
         <f>IFERROR(VLOOKUP(A48,Employee_Master!A:B,2,0),"")</f>
-        <v>Praveen Chandel</v>
+        <v>Gourav Rohilla</v>
       </c>
       <c r="C48" s="7" t="str">
         <f>IFERROR(VLOOKUP(A48,Employee_Master!A:B,3,0),"")</f>
@@ -39976,50 +39984,50 @@
       </c>
       <c r="D48" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A48,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A48,Participation_Entry!L:L))</f>
-        <v>52.891999999999996</v>
+        <v>52.176099999999998</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="6">
-        <v>451513</v>
+        <v>408627</v>
       </c>
       <c r="B49" s="7" t="str">
         <f>IFERROR(VLOOKUP(A49,Employee_Master!A:B,2,0),"")</f>
-        <v>Nishith Soni</v>
+        <v>Govind Rai</v>
       </c>
       <c r="C49" s="7" t="str">
         <f>IFERROR(VLOOKUP(A49,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D49" s="7" t="str">
+      <c r="D49" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A49,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A49,Participation_Entry!L:L))</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="6">
-        <v>468224</v>
+        <v>450436</v>
       </c>
       <c r="B50" s="7" t="str">
         <f>IFERROR(VLOOKUP(A50,Employee_Master!A:B,2,0),"")</f>
-        <v>Mohit Kumar</v>
+        <v>Govind Saini</v>
       </c>
       <c r="C50" s="7" t="str">
         <f>IFERROR(VLOOKUP(A50,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A50,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A50,Participation_Entry!L:L))</f>
-        <v>33.6372</v>
+        <v/>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="6">
-        <v>450256</v>
+        <v>463097</v>
       </c>
       <c r="B51" s="7" t="str">
         <f>IFERROR(VLOOKUP(A51,Employee_Master!A:B,2,0),"")</f>
-        <v>Jyotish  Patar</v>
+        <v>Gurkamalpreet Singh</v>
       </c>
       <c r="C51" s="7" t="str">
         <f>IFERROR(VLOOKUP(A51,Employee_Master!A:B,3,0),"")</f>
@@ -40027,16 +40035,16 @@
       </c>
       <c r="D51" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A51,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A51,Participation_Entry!L:L))</f>
-        <v>66.959599999999995</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="6">
-        <v>454456</v>
+        <v>435548</v>
       </c>
       <c r="B52" s="7" t="str">
         <f>IFERROR(VLOOKUP(A52,Employee_Master!A:B,2,0),"")</f>
-        <v>Akash Deshmukh</v>
+        <v>Gurwant Sran</v>
       </c>
       <c r="C52" s="7" t="str">
         <f>IFERROR(VLOOKUP(A52,Employee_Master!A:B,3,0),"")</f>
@@ -40044,16 +40052,16 @@
       </c>
       <c r="D52" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A52,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A52,Participation_Entry!L:L))</f>
-        <v>118.25749999999999</v>
+        <v>67.009199999999993</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="6">
-        <v>446300</v>
+        <v>448882</v>
       </c>
       <c r="B53" s="7" t="str">
         <f>IFERROR(VLOOKUP(A53,Employee_Master!A:B,2,0),"")</f>
-        <v>Simranjit Singh</v>
+        <v>Gurwinder Singh</v>
       </c>
       <c r="C53" s="7" t="str">
         <f>IFERROR(VLOOKUP(A53,Employee_Master!A:B,3,0),"")</f>
@@ -40061,33 +40069,33 @@
       </c>
       <c r="D53" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A53,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A53,Participation_Entry!L:L))</f>
-        <v>80.99799999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="6">
-        <v>459234</v>
+        <v>428544</v>
       </c>
       <c r="B54" s="7" t="str">
         <f>IFERROR(VLOOKUP(A54,Employee_Master!A:B,2,0),"")</f>
-        <v>Ritik Kumar</v>
+        <v>Harjot Singh</v>
       </c>
       <c r="C54" s="7" t="str">
         <f>IFERROR(VLOOKUP(A54,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D54" s="7" t="str">
+      <c r="D54" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A54,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A54,Participation_Entry!L:L))</f>
-        <v/>
+        <v>55.920200000000001</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="6">
-        <v>459464</v>
+        <v>479348</v>
       </c>
       <c r="B55" s="7" t="str">
         <f>IFERROR(VLOOKUP(A55,Employee_Master!A:B,2,0),"")</f>
-        <v>Manish Kumar Maury</v>
+        <v>Harmandeep</v>
       </c>
       <c r="C55" s="7" t="str">
         <f>IFERROR(VLOOKUP(A55,Employee_Master!A:B,3,0),"")</f>
@@ -40095,16 +40103,16 @@
       </c>
       <c r="D55" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A55,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A55,Participation_Entry!L:L))</f>
-        <v>30</v>
+        <v>20.955099999999998</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="6">
-        <v>457430</v>
+        <v>722183</v>
       </c>
       <c r="B56" s="7" t="str">
         <f>IFERROR(VLOOKUP(A56,Employee_Master!A:B,2,0),"")</f>
-        <v>Manish Kumar</v>
+        <v>Harpreet Kaur Malik</v>
       </c>
       <c r="C56" s="7" t="str">
         <f>IFERROR(VLOOKUP(A56,Employee_Master!A:B,3,0),"")</f>
@@ -40112,16 +40120,16 @@
       </c>
       <c r="D56" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A56,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A56,Participation_Entry!L:L))</f>
-        <v>100.7488</v>
+        <v>77.574700000000007</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="6">
-        <v>450436</v>
+        <v>452116</v>
       </c>
       <c r="B57" s="7" t="str">
         <f>IFERROR(VLOOKUP(A57,Employee_Master!A:B,2,0),"")</f>
-        <v>Govind Saini</v>
+        <v xml:space="preserve">Harsh </v>
       </c>
       <c r="C57" s="7" t="str">
         <f>IFERROR(VLOOKUP(A57,Employee_Master!A:B,3,0),"")</f>
@@ -40134,28 +40142,28 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="6">
-        <v>450694</v>
+        <v>487476</v>
       </c>
       <c r="B58" s="7" t="str">
         <f>IFERROR(VLOOKUP(A58,Employee_Master!A:B,2,0),"")</f>
-        <v>Kawaljot Kaur</v>
+        <v>Harshdeep Singh</v>
       </c>
       <c r="C58" s="7" t="str">
         <f>IFERROR(VLOOKUP(A58,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A58,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A58,Participation_Entry!L:L))</f>
-        <v>63.510199999999998</v>
+        <v/>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="6">
-        <v>450225</v>
+        <v>464193</v>
       </c>
       <c r="B59" s="7" t="str">
         <f>IFERROR(VLOOKUP(A59,Employee_Master!A:B,2,0),"")</f>
-        <v>Nikita</v>
+        <v>Hemant Singh</v>
       </c>
       <c r="C59" s="7" t="str">
         <f>IFERROR(VLOOKUP(A59,Employee_Master!A:B,3,0),"")</f>
@@ -40163,16 +40171,16 @@
       </c>
       <c r="D59" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A59,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A59,Participation_Entry!L:L))</f>
-        <v>33.176699999999997</v>
+        <v>59.4452</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="6">
-        <v>486309</v>
+        <v>464188</v>
       </c>
       <c r="B60" s="7" t="str">
         <f>IFERROR(VLOOKUP(A60,Employee_Master!A:B,2,0),"")</f>
-        <v>Ankit Bhatt</v>
+        <v>Himanshu Saini</v>
       </c>
       <c r="C60" s="7" t="str">
         <f>IFERROR(VLOOKUP(A60,Employee_Master!A:B,3,0),"")</f>
@@ -40180,16 +40188,16 @@
       </c>
       <c r="D60" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A60,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A60,Participation_Entry!L:L))</f>
-        <v>86.121200000000002</v>
+        <v>105.45070000000001</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="6">
-        <v>450228</v>
+        <v>437534</v>
       </c>
       <c r="B61" s="7" t="str">
         <f>IFERROR(VLOOKUP(A61,Employee_Master!A:B,2,0),"")</f>
-        <v>Shubham Sharma</v>
+        <v>Himanshu Sangar</v>
       </c>
       <c r="C61" s="7" t="str">
         <f>IFERROR(VLOOKUP(A61,Employee_Master!A:B,3,0),"")</f>
@@ -40197,16 +40205,16 @@
       </c>
       <c r="D61" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A61,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A61,Participation_Entry!L:L))</f>
-        <v>69.331400000000002</v>
+        <v>176.45569999999998</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="6">
-        <v>450437</v>
+        <v>460764</v>
       </c>
       <c r="B62" s="7" t="str">
         <f>IFERROR(VLOOKUP(A62,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Tinku Shekhawat </v>
+        <v>Himanshu Yadav</v>
       </c>
       <c r="C62" s="7" t="str">
         <f>IFERROR(VLOOKUP(A62,Employee_Master!A:B,3,0),"")</f>
@@ -40214,33 +40222,33 @@
       </c>
       <c r="D62" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A62,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A62,Participation_Entry!L:L))</f>
-        <v>47.703400000000002</v>
+        <v>78.929700000000011</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="6">
-        <v>450693</v>
+        <v>479724</v>
       </c>
       <c r="B63" s="7" t="str">
         <f>IFERROR(VLOOKUP(A63,Employee_Master!A:B,2,0),"")</f>
-        <v>Sagar rana</v>
+        <v>Honey</v>
       </c>
       <c r="C63" s="7" t="str">
         <f>IFERROR(VLOOKUP(A63,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D63" s="7" t="str">
+      <c r="D63" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A63,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A63,Participation_Entry!L:L))</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="6">
-        <v>452073</v>
+        <v>478270</v>
       </c>
       <c r="B64" s="7" t="str">
         <f>IFERROR(VLOOKUP(A64,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Aashish </v>
+        <v xml:space="preserve">Inzmam Ali </v>
       </c>
       <c r="C64" s="7" t="str">
         <f>IFERROR(VLOOKUP(A64,Employee_Master!A:B,3,0),"")</f>
@@ -40248,16 +40256,16 @@
       </c>
       <c r="D64" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A64,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A64,Participation_Entry!L:L))</f>
-        <v>63.355499999999999</v>
+        <v>20.583300000000001</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="6">
-        <v>451857</v>
+        <v>478377</v>
       </c>
       <c r="B65" s="7" t="str">
         <f>IFERROR(VLOOKUP(A65,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Amar Kumar </v>
+        <v xml:space="preserve">Ishi Verma </v>
       </c>
       <c r="C65" s="7" t="str">
         <f>IFERROR(VLOOKUP(A65,Employee_Master!A:B,3,0),"")</f>
@@ -40265,16 +40273,16 @@
       </c>
       <c r="D65" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A65,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A65,Participation_Entry!L:L))</f>
-        <v>64.830199999999991</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="6">
-        <v>451858</v>
+        <v>458702</v>
       </c>
       <c r="B66" s="7" t="str">
         <f>IFERROR(VLOOKUP(A66,Employee_Master!A:B,2,0),"")</f>
-        <v>Ankit Bhardwaj</v>
+        <v>Jasbeer Singh</v>
       </c>
       <c r="C66" s="7" t="str">
         <f>IFERROR(VLOOKUP(A66,Employee_Master!A:B,3,0),"")</f>
@@ -40282,16 +40290,16 @@
       </c>
       <c r="D66" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A66,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A66,Participation_Entry!L:L))</f>
-        <v>34.916600000000003</v>
+        <v>103.7077</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="6">
-        <v>452115</v>
+        <v>473266</v>
       </c>
       <c r="B67" s="7" t="str">
         <f>IFERROR(VLOOKUP(A67,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Anshul Sharma </v>
+        <v>Jitender Yadav</v>
       </c>
       <c r="C67" s="7" t="str">
         <f>IFERROR(VLOOKUP(A67,Employee_Master!A:B,3,0),"")</f>
@@ -40299,16 +40307,16 @@
       </c>
       <c r="D67" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A67,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A67,Participation_Entry!L:L))</f>
-        <v>30</v>
+        <v>45.494999999999997</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="6">
-        <v>452056</v>
+        <v>710555</v>
       </c>
       <c r="B68" s="7" t="str">
         <f>IFERROR(VLOOKUP(A68,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Rupesh </v>
+        <v>Jyoti Chauhan</v>
       </c>
       <c r="C68" s="7" t="str">
         <f>IFERROR(VLOOKUP(A68,Employee_Master!A:B,3,0),"")</f>
@@ -40316,16 +40324,16 @@
       </c>
       <c r="D68" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A68,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A68,Participation_Entry!L:L))</f>
-        <v>105.39600000000002</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="6">
-        <v>452057</v>
+        <v>710013</v>
       </c>
       <c r="B69" s="7" t="str">
         <f>IFERROR(VLOOKUP(A69,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Sahil Thakur </v>
+        <v>Jyoti Saini</v>
       </c>
       <c r="C69" s="7" t="str">
         <f>IFERROR(VLOOKUP(A69,Employee_Master!A:B,3,0),"")</f>
@@ -40333,16 +40341,16 @@
       </c>
       <c r="D69" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A69,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A69,Participation_Entry!L:L))</f>
-        <v>30</v>
+        <v>66.440899999999999</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="6">
-        <v>452119</v>
+        <v>450256</v>
       </c>
       <c r="B70" s="7" t="str">
         <f>IFERROR(VLOOKUP(A70,Employee_Master!A:B,2,0),"")</f>
-        <v>Akhil Tiwari</v>
+        <v>Jyotish  Patar</v>
       </c>
       <c r="C70" s="7" t="str">
         <f>IFERROR(VLOOKUP(A70,Employee_Master!A:B,3,0),"")</f>
@@ -40350,16 +40358,16 @@
       </c>
       <c r="D70" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A70,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A70,Participation_Entry!L:L))</f>
-        <v>80.690899999999999</v>
+        <v>66.959599999999995</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="6">
-        <v>452058</v>
+        <v>436468</v>
       </c>
       <c r="B71" s="7" t="str">
         <f>IFERROR(VLOOKUP(A71,Employee_Master!A:B,2,0),"")</f>
-        <v>Bhavya Gupta</v>
+        <v>Karan Singh</v>
       </c>
       <c r="C71" s="7" t="str">
         <f>IFERROR(VLOOKUP(A71,Employee_Master!A:B,3,0),"")</f>
@@ -40367,16 +40375,16 @@
       </c>
       <c r="D71" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A71,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A71,Participation_Entry!L:L))</f>
-        <v>70.827600000000004</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="6">
-        <v>452075</v>
+        <v>463833</v>
       </c>
       <c r="B72" s="7" t="str">
         <f>IFERROR(VLOOKUP(A72,Employee_Master!A:B,2,0),"")</f>
-        <v>Mansi Yadav</v>
+        <v>Kartik Shakya</v>
       </c>
       <c r="C72" s="7" t="str">
         <f>IFERROR(VLOOKUP(A72,Employee_Master!A:B,3,0),"")</f>
@@ -40384,16 +40392,16 @@
       </c>
       <c r="D72" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A72,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A72,Participation_Entry!L:L))</f>
-        <v>30</v>
+        <v>124.9906</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="6">
-        <v>452121</v>
+        <v>709664</v>
       </c>
       <c r="B73" s="7" t="str">
         <f>IFERROR(VLOOKUP(A73,Employee_Master!A:B,2,0),"")</f>
-        <v>Nishi Singh</v>
+        <v>Kavita Rathore</v>
       </c>
       <c r="C73" s="7" t="str">
         <f>IFERROR(VLOOKUP(A73,Employee_Master!A:B,3,0),"")</f>
@@ -40401,16 +40409,16 @@
       </c>
       <c r="D73" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A73,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A73,Participation_Entry!L:L))</f>
-        <v>55.396699999999996</v>
+        <v>55.380699999999997</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="6">
-        <v>452118</v>
+        <v>450694</v>
       </c>
       <c r="B74" s="7" t="str">
         <f>IFERROR(VLOOKUP(A74,Employee_Master!A:B,2,0),"")</f>
-        <v>Riya Kumari</v>
+        <v>Kawaljot Kaur</v>
       </c>
       <c r="C74" s="7" t="str">
         <f>IFERROR(VLOOKUP(A74,Employee_Master!A:B,3,0),"")</f>
@@ -40418,16 +40426,16 @@
       </c>
       <c r="D74" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A74,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A74,Participation_Entry!L:L))</f>
-        <v>59.468599999999995</v>
+        <v>63.510199999999998</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="6">
-        <v>452991</v>
+        <v>416828</v>
       </c>
       <c r="B75" s="7" t="str">
         <f>IFERROR(VLOOKUP(A75,Employee_Master!A:B,2,0),"")</f>
-        <v>Gourav Rohilla</v>
+        <v>Keshav Dev</v>
       </c>
       <c r="C75" s="7" t="str">
         <f>IFERROR(VLOOKUP(A75,Employee_Master!A:B,3,0),"")</f>
@@ -40435,16 +40443,16 @@
       </c>
       <c r="D75" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A75,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A75,Participation_Entry!L:L))</f>
-        <v>52.176099999999998</v>
+        <v>110.72030000000001</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="6">
-        <v>453089</v>
+      <c r="A76" s="15">
+        <v>396485</v>
       </c>
       <c r="B76" s="7" t="str">
         <f>IFERROR(VLOOKUP(A76,Employee_Master!A:B,2,0),"")</f>
-        <v>Arun Lamba</v>
+        <v>Khushbir Singh</v>
       </c>
       <c r="C76" s="7" t="str">
         <f>IFERROR(VLOOKUP(A76,Employee_Master!A:B,3,0),"")</f>
@@ -40452,33 +40460,33 @@
       </c>
       <c r="D76" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A76,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A76,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>129.6858</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="6">
-        <v>460627</v>
+        <v>721899</v>
       </c>
       <c r="B77" s="7" t="str">
         <f>IFERROR(VLOOKUP(A77,Employee_Master!A:B,2,0),"")</f>
-        <v>Sushil</v>
+        <v>Khushboo Yadav</v>
       </c>
       <c r="C77" s="7" t="str">
         <f>IFERROR(VLOOKUP(A77,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D77" s="7" t="str">
+      <c r="D77" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A77,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A77,Participation_Entry!L:L))</f>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="6">
-        <v>460628</v>
+        <v>449891</v>
       </c>
       <c r="B78" s="7" t="str">
         <f>IFERROR(VLOOKUP(A78,Employee_Master!A:B,2,0),"")</f>
-        <v>Smarth</v>
+        <v>Komalpreet</v>
       </c>
       <c r="C78" s="7" t="str">
         <f>IFERROR(VLOOKUP(A78,Employee_Master!A:B,3,0),"")</f>
@@ -40486,16 +40494,16 @@
       </c>
       <c r="D78" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A78,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A78,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>119.6532</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="6">
-        <v>461161</v>
+        <v>722393</v>
       </c>
       <c r="B79" s="7" t="str">
         <f>IFERROR(VLOOKUP(A79,Employee_Master!A:B,2,0),"")</f>
-        <v>Abhay Singh</v>
+        <v>Koteswara Devireddy</v>
       </c>
       <c r="C79" s="7" t="str">
         <f>IFERROR(VLOOKUP(A79,Employee_Master!A:B,3,0),"")</f>
@@ -40503,16 +40511,16 @@
       </c>
       <c r="D79" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A79,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A79,Participation_Entry!L:L))</f>
-        <v>42.836399999999998</v>
+        <v>113.37639999999999</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="6">
-        <v>463097</v>
+        <v>440620</v>
       </c>
       <c r="B80" s="7" t="str">
         <f>IFERROR(VLOOKUP(A80,Employee_Master!A:B,2,0),"")</f>
-        <v>Gurkamalpreet Singh</v>
+        <v>Kuldeep Singh</v>
       </c>
       <c r="C80" s="7" t="str">
         <f>IFERROR(VLOOKUP(A80,Employee_Master!A:B,3,0),"")</f>
@@ -40520,16 +40528,16 @@
       </c>
       <c r="D80" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A80,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A80,Participation_Entry!L:L))</f>
-        <v>20</v>
+        <v>83.278599999999997</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="6">
-        <v>463833</v>
+        <v>476372</v>
       </c>
       <c r="B81" s="7" t="str">
         <f>IFERROR(VLOOKUP(A81,Employee_Master!A:B,2,0),"")</f>
-        <v>Kartik Shakya</v>
+        <v>Laksh</v>
       </c>
       <c r="C81" s="7" t="str">
         <f>IFERROR(VLOOKUP(A81,Employee_Master!A:B,3,0),"")</f>
@@ -40537,16 +40545,16 @@
       </c>
       <c r="D81" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A81,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A81,Participation_Entry!L:L))</f>
-        <v>124.9906</v>
+        <v>74.443899999999999</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="6">
-        <v>464193</v>
+        <v>450224</v>
       </c>
       <c r="B82" s="7" t="str">
         <f>IFERROR(VLOOKUP(A82,Employee_Master!A:B,2,0),"")</f>
-        <v>Hemant Singh</v>
+        <v>Lalit Nagar</v>
       </c>
       <c r="C82" s="7" t="str">
         <f>IFERROR(VLOOKUP(A82,Employee_Master!A:B,3,0),"")</f>
@@ -40554,16 +40562,16 @@
       </c>
       <c r="D82" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A82,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A82,Participation_Entry!L:L))</f>
-        <v>59.4452</v>
+        <v>29.381999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="6">
-        <v>452074</v>
+        <v>460284</v>
       </c>
       <c r="B83" s="7" t="str">
         <f>IFERROR(VLOOKUP(A83,Employee_Master!A:B,2,0),"")</f>
-        <v>Sneha Singh</v>
+        <v>Madhu Aggu</v>
       </c>
       <c r="C83" s="7" t="str">
         <f>IFERROR(VLOOKUP(A83,Employee_Master!A:B,3,0),"")</f>
@@ -40571,16 +40579,16 @@
       </c>
       <c r="D83" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A83,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A83,Participation_Entry!L:L))</f>
-        <v>36.646599999999999</v>
+        <v>62.599800000000002</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="6">
-        <v>465254</v>
+        <v>452059</v>
       </c>
       <c r="B84" s="7" t="str">
         <f>IFERROR(VLOOKUP(A84,Employee_Master!A:B,2,0),"")</f>
-        <v>Narender Kumar</v>
+        <v>Mahi Singh</v>
       </c>
       <c r="C84" s="7" t="str">
         <f>IFERROR(VLOOKUP(A84,Employee_Master!A:B,3,0),"")</f>
@@ -40588,33 +40596,33 @@
       </c>
       <c r="D84" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A84,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A84,Participation_Entry!L:L))</f>
-        <v>77.589300000000009</v>
+        <v>38.909199999999998</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="6">
-        <v>467075</v>
+        <v>457795</v>
       </c>
       <c r="B85" s="7" t="str">
         <f>IFERROR(VLOOKUP(A85,Employee_Master!A:B,2,0),"")</f>
-        <v>Ritish</v>
+        <v>Manbir Sain</v>
       </c>
       <c r="C85" s="7" t="str">
         <f>IFERROR(VLOOKUP(A85,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D85" s="7" t="str">
+      <c r="D85" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A85,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A85,Participation_Entry!L:L))</f>
-        <v/>
+        <v>20.002700000000001</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="6">
-        <v>465255</v>
+        <v>434518</v>
       </c>
       <c r="B86" s="7" t="str">
         <f>IFERROR(VLOOKUP(A86,Employee_Master!A:B,2,0),"")</f>
-        <v>Mukul Suman</v>
+        <v>Maneesh Mohan</v>
       </c>
       <c r="C86" s="7" t="str">
         <f>IFERROR(VLOOKUP(A86,Employee_Master!A:B,3,0),"")</f>
@@ -40622,16 +40630,16 @@
       </c>
       <c r="D86" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A86,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A86,Participation_Entry!L:L))</f>
-        <v>109.57489999999999</v>
+        <v>82.684799999999996</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="6">
-        <v>467068</v>
+        <v>450030</v>
       </c>
       <c r="B87" s="7" t="str">
         <f>IFERROR(VLOOKUP(A87,Employee_Master!A:B,2,0),"")</f>
-        <v>Anuj Kumar</v>
+        <v xml:space="preserve">Manish bisht </v>
       </c>
       <c r="C87" s="7" t="str">
         <f>IFERROR(VLOOKUP(A87,Employee_Master!A:B,3,0),"")</f>
@@ -40639,67 +40647,67 @@
       </c>
       <c r="D87" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A87,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A87,Participation_Entry!L:L))</f>
-        <v>79.665700000000001</v>
+        <v>99.593899999999991</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="6">
-        <v>467915</v>
+        <v>487107</v>
       </c>
       <c r="B88" s="7" t="str">
         <f>IFERROR(VLOOKUP(A88,Employee_Master!A:B,2,0),"")</f>
-        <v>Rahul Kinkar</v>
+        <v>Manish Kr. Singh</v>
       </c>
       <c r="C88" s="7" t="str">
         <f>IFERROR(VLOOKUP(A88,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D88" s="7" t="str">
+      <c r="D88" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A88,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A88,Participation_Entry!L:L))</f>
-        <v/>
+        <v>53.0854</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="6">
-        <v>468536</v>
+        <v>452799</v>
       </c>
       <c r="B89" s="7" t="str">
         <f>IFERROR(VLOOKUP(A89,Employee_Master!A:B,2,0),"")</f>
-        <v>Vinod Kumar</v>
+        <v>Manish Kukreti</v>
       </c>
       <c r="C89" s="7" t="str">
         <f>IFERROR(VLOOKUP(A89,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D89" s="7" t="str">
+      <c r="D89" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A89,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A89,Participation_Entry!L:L))</f>
-        <v/>
+        <v>111.68900000000001</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="6">
-        <v>468456</v>
+        <v>433939</v>
       </c>
       <c r="B90" s="7" t="str">
         <f>IFERROR(VLOOKUP(A90,Employee_Master!A:B,2,0),"")</f>
-        <v>Ayush Joshi</v>
+        <v>Manish Kumar</v>
       </c>
       <c r="C90" s="7" t="str">
         <f>IFERROR(VLOOKUP(A90,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D90" s="7" t="str">
+      <c r="D90" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A90,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A90,Participation_Entry!L:L))</f>
-        <v/>
+        <v>47.6008</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="6">
-        <v>469899</v>
+        <v>457430</v>
       </c>
       <c r="B91" s="7" t="str">
         <f>IFERROR(VLOOKUP(A91,Employee_Master!A:B,2,0),"")</f>
-        <v>Ankit</v>
+        <v>Manish Kumar</v>
       </c>
       <c r="C91" s="7" t="str">
         <f>IFERROR(VLOOKUP(A91,Employee_Master!A:B,3,0),"")</f>
@@ -40707,16 +40715,16 @@
       </c>
       <c r="D91" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A91,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A91,Participation_Entry!L:L))</f>
-        <v>20</v>
+        <v>100.7488</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="6">
-        <v>468660</v>
+        <v>459464</v>
       </c>
       <c r="B92" s="7" t="str">
         <f>IFERROR(VLOOKUP(A92,Employee_Master!A:B,2,0),"")</f>
-        <v>Samay Raj</v>
+        <v>Manish Kumar Maury</v>
       </c>
       <c r="C92" s="7" t="str">
         <f>IFERROR(VLOOKUP(A92,Employee_Master!A:B,3,0),"")</f>
@@ -40724,33 +40732,33 @@
       </c>
       <c r="D92" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A92,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A92,Participation_Entry!L:L))</f>
-        <v>115.3021</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="6">
-        <v>469627</v>
+        <v>458749</v>
       </c>
       <c r="B93" s="7" t="str">
         <f>IFERROR(VLOOKUP(A93,Employee_Master!A:B,2,0),"")</f>
-        <v>Rahul Kumar</v>
+        <v>Manoj Kumar Jangra</v>
       </c>
       <c r="C93" s="7" t="str">
         <f>IFERROR(VLOOKUP(A93,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D93" s="7" t="str">
+      <c r="D93" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A93,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A93,Participation_Entry!L:L))</f>
-        <v/>
+        <v>55.865300000000005</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="6">
-        <v>469617</v>
+        <v>416087</v>
       </c>
       <c r="B94" s="7" t="str">
         <f>IFERROR(VLOOKUP(A94,Employee_Master!A:B,2,0),"")</f>
-        <v>Siyaram</v>
+        <v>Manoj Singh</v>
       </c>
       <c r="C94" s="7" t="str">
         <f>IFERROR(VLOOKUP(A94,Employee_Master!A:B,3,0),"")</f>
@@ -40758,16 +40766,16 @@
       </c>
       <c r="D94" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A94,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A94,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="6">
-        <v>472322</v>
+        <v>450171</v>
       </c>
       <c r="B95" s="7" t="str">
         <f>IFERROR(VLOOKUP(A95,Employee_Master!A:B,2,0),"")</f>
-        <v>Sanjeet Kumar</v>
+        <v>Manpreet Kaur</v>
       </c>
       <c r="C95" s="7" t="str">
         <f>IFERROR(VLOOKUP(A95,Employee_Master!A:B,3,0),"")</f>
@@ -40775,16 +40783,16 @@
       </c>
       <c r="D95" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A95,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A95,Participation_Entry!L:L))</f>
-        <v>68.516800000000003</v>
+        <v>69.037800000000004</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="6">
-        <v>478377</v>
+        <v>452075</v>
       </c>
       <c r="B96" s="7" t="str">
         <f>IFERROR(VLOOKUP(A96,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Ishi Verma </v>
+        <v>Mansi Yadav</v>
       </c>
       <c r="C96" s="7" t="str">
         <f>IFERROR(VLOOKUP(A96,Employee_Master!A:B,3,0),"")</f>
@@ -40792,16 +40800,16 @@
       </c>
       <c r="D96" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A96,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A96,Participation_Entry!L:L))</f>
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="6">
-        <v>478308</v>
+      <c r="A97" s="15">
+        <v>460692</v>
       </c>
       <c r="B97" s="7" t="str">
         <f>IFERROR(VLOOKUP(A97,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Abhishek savita </v>
+        <v>Mayank Arya</v>
       </c>
       <c r="C97" s="7" t="str">
         <f>IFERROR(VLOOKUP(A97,Employee_Master!A:B,3,0),"")</f>
@@ -40809,16 +40817,16 @@
       </c>
       <c r="D97" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A97,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A97,Participation_Entry!L:L))</f>
-        <v>88.970200000000006</v>
+        <v>74.301100000000005</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="6">
-        <v>478270</v>
+        <v>440774</v>
       </c>
       <c r="B98" s="7" t="str">
         <f>IFERROR(VLOOKUP(A98,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Inzmam Ali </v>
+        <v>Mehnga Singh</v>
       </c>
       <c r="C98" s="7" t="str">
         <f>IFERROR(VLOOKUP(A98,Employee_Master!A:B,3,0),"")</f>
@@ -40826,16 +40834,16 @@
       </c>
       <c r="D98" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A98,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A98,Participation_Entry!L:L))</f>
-        <v>20.583300000000001</v>
+        <v>42.507199999999997</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="6">
-        <v>479348</v>
+        <v>468224</v>
       </c>
       <c r="B99" s="7" t="str">
         <f>IFERROR(VLOOKUP(A99,Employee_Master!A:B,2,0),"")</f>
-        <v>Harmandeep</v>
+        <v>Mohit Kumar</v>
       </c>
       <c r="C99" s="7" t="str">
         <f>IFERROR(VLOOKUP(A99,Employee_Master!A:B,3,0),"")</f>
@@ -40843,16 +40851,16 @@
       </c>
       <c r="D99" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A99,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A99,Participation_Entry!L:L))</f>
-        <v>20.955099999999998</v>
+        <v>33.6372</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="6">
-        <v>479724</v>
+        <v>464871</v>
       </c>
       <c r="B100" s="7" t="str">
         <f>IFERROR(VLOOKUP(A100,Employee_Master!A:B,2,0),"")</f>
-        <v>Honey</v>
+        <v>Mohit Sahu</v>
       </c>
       <c r="C100" s="7" t="str">
         <f>IFERROR(VLOOKUP(A100,Employee_Master!A:B,3,0),"")</f>
@@ -40860,33 +40868,33 @@
       </c>
       <c r="D100" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A100,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A100,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>92.456299999999999</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="6">
-        <v>487476</v>
+        <v>465255</v>
       </c>
       <c r="B101" s="7" t="str">
         <f>IFERROR(VLOOKUP(A101,Employee_Master!A:B,2,0),"")</f>
-        <v>Harshdeep Singh</v>
+        <v>Mukul Suman</v>
       </c>
       <c r="C101" s="7" t="str">
         <f>IFERROR(VLOOKUP(A101,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D101" s="7" t="str">
+      <c r="D101" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A101,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A101,Participation_Entry!L:L))</f>
-        <v/>
+        <v>109.57489999999999</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="6">
-        <v>396485</v>
+        <v>465254</v>
       </c>
       <c r="B102" s="7" t="str">
         <f>IFERROR(VLOOKUP(A102,Employee_Master!A:B,2,0),"")</f>
-        <v>Khushbir Singh</v>
+        <v>Narender Kumar</v>
       </c>
       <c r="C102" s="7" t="str">
         <f>IFERROR(VLOOKUP(A102,Employee_Master!A:B,3,0),"")</f>
@@ -40894,16 +40902,16 @@
       </c>
       <c r="D102" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A102,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A102,Participation_Entry!L:L))</f>
-        <v>129.6858</v>
+        <v>77.589300000000009</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="6">
-        <v>432865</v>
+        <v>424332</v>
       </c>
       <c r="B103" s="7" t="str">
         <f>IFERROR(VLOOKUP(A103,Employee_Master!A:B,2,0),"")</f>
-        <v>Rupesh Gandhi</v>
+        <v>Naresh Kumar</v>
       </c>
       <c r="C103" s="7" t="str">
         <f>IFERROR(VLOOKUP(A103,Employee_Master!A:B,3,0),"")</f>
@@ -40911,16 +40919,16 @@
       </c>
       <c r="D103" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A103,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A103,Participation_Entry!L:L))</f>
-        <v>70.215699999999998</v>
+        <v>86.822200000000009</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="6">
-        <v>447836</v>
+        <v>716610</v>
       </c>
       <c r="B104" s="7" t="str">
         <f>IFERROR(VLOOKUP(A104,Employee_Master!A:B,2,0),"")</f>
-        <v>Rakesh S</v>
+        <v>Naval Singh</v>
       </c>
       <c r="C104" s="7" t="str">
         <f>IFERROR(VLOOKUP(A104,Employee_Master!A:B,3,0),"")</f>
@@ -40928,16 +40936,16 @@
       </c>
       <c r="D104" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A104,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A104,Participation_Entry!L:L))</f>
-        <v>29.249499999999998</v>
+        <v>108.3938</v>
       </c>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="6">
-        <v>449635</v>
+      <c r="A105" s="15">
+        <v>453949</v>
       </c>
       <c r="B105" s="7" t="str">
         <f>IFERROR(VLOOKUP(A105,Employee_Master!A:B,2,0),"")</f>
-        <v>Sushma Tiwari</v>
+        <v>Naveen Kumar</v>
       </c>
       <c r="C105" s="7" t="str">
         <f>IFERROR(VLOOKUP(A105,Employee_Master!A:B,3,0),"")</f>
@@ -40945,16 +40953,16 @@
       </c>
       <c r="D105" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A105,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A105,Participation_Entry!L:L))</f>
-        <v>68.346299999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="6">
-        <v>440774</v>
+        <v>471387</v>
       </c>
       <c r="B106" s="7" t="str">
         <f>IFERROR(VLOOKUP(A106,Employee_Master!A:B,2,0),"")</f>
-        <v>Mehnga Singh</v>
+        <v>Neeraj</v>
       </c>
       <c r="C106" s="7" t="str">
         <f>IFERROR(VLOOKUP(A106,Employee_Master!A:B,3,0),"")</f>
@@ -40962,16 +40970,16 @@
       </c>
       <c r="D106" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A106,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A106,Participation_Entry!L:L))</f>
-        <v>42.507199999999997</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="6">
-        <v>460513</v>
+      <c r="A107" s="15">
+        <v>488518</v>
       </c>
       <c r="B107" s="7" t="str">
         <f>IFERROR(VLOOKUP(A107,Employee_Master!A:B,2,0),"")</f>
-        <v>Dinesh Kumar</v>
+        <v>Neha Chaturvedi</v>
       </c>
       <c r="C107" s="7" t="str">
         <f>IFERROR(VLOOKUP(A107,Employee_Master!A:B,3,0),"")</f>
@@ -40979,16 +40987,16 @@
       </c>
       <c r="D107" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A107,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A107,Participation_Entry!L:L))</f>
-        <v>60.249700000000004</v>
+        <v>33.218600000000002</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="6">
-        <v>458749</v>
+        <v>450225</v>
       </c>
       <c r="B108" s="7" t="str">
         <f>IFERROR(VLOOKUP(A108,Employee_Master!A:B,2,0),"")</f>
-        <v>Manoj Kumar Jangra</v>
+        <v>Nikita</v>
       </c>
       <c r="C108" s="7" t="str">
         <f>IFERROR(VLOOKUP(A108,Employee_Master!A:B,3,0),"")</f>
@@ -40996,16 +41004,16 @@
       </c>
       <c r="D108" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A108,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A108,Participation_Entry!L:L))</f>
-        <v>55.865300000000005</v>
+        <v>33.176699999999997</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="6">
-        <v>458702</v>
+        <v>452121</v>
       </c>
       <c r="B109" s="7" t="str">
         <f>IFERROR(VLOOKUP(A109,Employee_Master!A:B,2,0),"")</f>
-        <v>Jasbeer Singh</v>
+        <v>Nishi Singh</v>
       </c>
       <c r="C109" s="7" t="str">
         <f>IFERROR(VLOOKUP(A109,Employee_Master!A:B,3,0),"")</f>
@@ -41013,33 +41021,33 @@
       </c>
       <c r="D109" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A109,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A109,Participation_Entry!L:L))</f>
-        <v>103.7077</v>
+        <v>55.396699999999996</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="6">
-        <v>449890</v>
+        <v>451513</v>
       </c>
       <c r="B110" s="7" t="str">
         <f>IFERROR(VLOOKUP(A110,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Ashish Baghel </v>
+        <v>Nishith Soni</v>
       </c>
       <c r="C110" s="7" t="str">
         <f>IFERROR(VLOOKUP(A110,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D110" s="7">
+      <c r="D110" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A110,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A110,Participation_Entry!L:L))</f>
-        <v>50.825800000000001</v>
+        <v/>
       </c>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="6">
-        <v>450030</v>
+      <c r="A111" s="15">
+        <v>435877</v>
       </c>
       <c r="B111" s="7" t="str">
         <f>IFERROR(VLOOKUP(A111,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Manish bisht </v>
+        <v>Pardeep Kumar</v>
       </c>
       <c r="C111" s="7" t="str">
         <f>IFERROR(VLOOKUP(A111,Employee_Master!A:B,3,0),"")</f>
@@ -41047,50 +41055,50 @@
       </c>
       <c r="D111" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A111,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A111,Participation_Entry!L:L))</f>
-        <v>99.593899999999991</v>
+        <v>19.581299999999999</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="6">
-        <v>450325</v>
+        <v>445891</v>
       </c>
       <c r="B112" s="7" t="str">
         <f>IFERROR(VLOOKUP(A112,Employee_Master!A:B,2,0),"")</f>
-        <v>Simratpal Singh</v>
+        <v>Parmvir Singh</v>
       </c>
       <c r="C112" s="7" t="str">
         <f>IFERROR(VLOOKUP(A112,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D112" s="7" t="str">
+      <c r="D112" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A112,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A112,Participation_Entry!L:L))</f>
-        <v/>
+        <v>32.670700000000004</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="6">
-        <v>452116</v>
+        <v>473015</v>
       </c>
       <c r="B113" s="7" t="str">
         <f>IFERROR(VLOOKUP(A113,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Harsh </v>
+        <v>Partap</v>
       </c>
       <c r="C113" s="7" t="str">
         <f>IFERROR(VLOOKUP(A113,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D113" s="7" t="str">
+      <c r="D113" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A113,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A113,Participation_Entry!L:L))</f>
-        <v/>
+        <v>40.225200000000001</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="6">
-        <v>457157</v>
+        <v>463059</v>
       </c>
       <c r="B114" s="7" t="str">
         <f>IFERROR(VLOOKUP(A114,Employee_Master!A:B,2,0),"")</f>
-        <v>Sachin Kashyap</v>
+        <v>Parvinder</v>
       </c>
       <c r="C114" s="7" t="str">
         <f>IFERROR(VLOOKUP(A114,Employee_Master!A:B,3,0),"")</f>
@@ -41098,16 +41106,16 @@
       </c>
       <c r="D114" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A114,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A114,Participation_Entry!L:L))</f>
-        <v>182.5196</v>
+        <v>71.264399999999995</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="6">
-        <v>456706</v>
+        <v>468887</v>
       </c>
       <c r="B115" s="7" t="str">
         <f>IFERROR(VLOOKUP(A115,Employee_Master!A:B,2,0),"")</f>
-        <v>Daljit Singh</v>
+        <v>Prachi Shukla</v>
       </c>
       <c r="C115" s="7" t="str">
         <f>IFERROR(VLOOKUP(A115,Employee_Master!A:B,3,0),"")</f>
@@ -41115,16 +41123,16 @@
       </c>
       <c r="D115" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A115,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A115,Participation_Entry!L:L))</f>
-        <v>12.424099999999999</v>
+        <v>23.021100000000001</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="6">
-        <v>457795</v>
+        <v>484877</v>
       </c>
       <c r="B116" s="7" t="str">
         <f>IFERROR(VLOOKUP(A116,Employee_Master!A:B,2,0),"")</f>
-        <v>Manbir Sain</v>
+        <v>Prashant Gupta</v>
       </c>
       <c r="C116" s="7" t="str">
         <f>IFERROR(VLOOKUP(A116,Employee_Master!A:B,3,0),"")</f>
@@ -41132,33 +41140,33 @@
       </c>
       <c r="D116" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A116,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A116,Participation_Entry!L:L))</f>
-        <v>20.002700000000001</v>
+        <v>47.981999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="6">
-        <v>460888</v>
+        <v>440317</v>
       </c>
       <c r="B117" s="7" t="str">
         <f>IFERROR(VLOOKUP(A117,Employee_Master!A:B,2,0),"")</f>
-        <v>Yatin</v>
+        <v>Praveen Chandel</v>
       </c>
       <c r="C117" s="7" t="str">
         <f>IFERROR(VLOOKUP(A117,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D117" s="7" t="str">
+      <c r="D117" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A117,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A117,Participation_Entry!L:L))</f>
-        <v/>
+        <v>52.891999999999996</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="6">
-        <v>460764</v>
+        <v>707131</v>
       </c>
       <c r="B118" s="7" t="str">
         <f>IFERROR(VLOOKUP(A118,Employee_Master!A:B,2,0),"")</f>
-        <v>Himanshu Yadav</v>
+        <v>Puja Bhalotia</v>
       </c>
       <c r="C118" s="7" t="str">
         <f>IFERROR(VLOOKUP(A118,Employee_Master!A:B,3,0),"")</f>
@@ -41166,67 +41174,67 @@
       </c>
       <c r="D118" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A118,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A118,Participation_Entry!L:L))</f>
-        <v>78.929700000000011</v>
+        <v>53.310899999999997</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="6">
-        <v>464871</v>
+        <v>467915</v>
       </c>
       <c r="B119" s="7" t="str">
         <f>IFERROR(VLOOKUP(A119,Employee_Master!A:B,2,0),"")</f>
-        <v>Mohit Sahu</v>
+        <v>Rahul Kinkar</v>
       </c>
       <c r="C119" s="7" t="str">
         <f>IFERROR(VLOOKUP(A119,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D119" s="7">
+      <c r="D119" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A119,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A119,Participation_Entry!L:L))</f>
-        <v>92.456299999999999</v>
+        <v/>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="6">
-        <v>466367</v>
+        <v>469627</v>
       </c>
       <c r="B120" s="7" t="str">
         <f>IFERROR(VLOOKUP(A120,Employee_Master!A:B,2,0),"")</f>
-        <v>Arjun Sharma</v>
+        <v>Rahul Kumar</v>
       </c>
       <c r="C120" s="7" t="str">
         <f>IFERROR(VLOOKUP(A120,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D120" s="7">
+      <c r="D120" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A120,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A120,Participation_Entry!L:L))</f>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="6">
-        <v>466562</v>
+        <v>438864</v>
       </c>
       <c r="B121" s="7" t="str">
         <f>IFERROR(VLOOKUP(A121,Employee_Master!A:B,2,0),"")</f>
-        <v>Vikas Bhardwaj</v>
+        <v>Rajan Gupta</v>
       </c>
       <c r="C121" s="7" t="str">
         <f>IFERROR(VLOOKUP(A121,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D121" s="7" t="str">
+      <c r="D121" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A121,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A121,Participation_Entry!L:L))</f>
-        <v/>
+        <v>53.038200000000003</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="6">
-        <v>466445</v>
+        <v>447836</v>
       </c>
       <c r="B122" s="7" t="str">
         <f>IFERROR(VLOOKUP(A122,Employee_Master!A:B,2,0),"")</f>
-        <v>Ayush Kumar</v>
+        <v>Rakesh S</v>
       </c>
       <c r="C122" s="7" t="str">
         <f>IFERROR(VLOOKUP(A122,Employee_Master!A:B,3,0),"")</f>
@@ -41234,16 +41242,16 @@
       </c>
       <c r="D122" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A122,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A122,Participation_Entry!L:L))</f>
-        <v>65.553899999999999</v>
+        <v>29.249499999999998</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="6">
-        <v>468157</v>
+        <v>449551</v>
       </c>
       <c r="B123" s="7" t="str">
         <f>IFERROR(VLOOKUP(A123,Employee_Master!A:B,2,0),"")</f>
-        <v>Ankit Tiwari</v>
+        <v>Ramesh Kumar</v>
       </c>
       <c r="C123" s="7" t="str">
         <f>IFERROR(VLOOKUP(A123,Employee_Master!A:B,3,0),"")</f>
@@ -41251,16 +41259,16 @@
       </c>
       <c r="D123" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A123,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A123,Participation_Entry!L:L))</f>
-        <v>48.702200000000005</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="6">
-        <v>473015</v>
+        <v>438957</v>
       </c>
       <c r="B124" s="7" t="str">
         <f>IFERROR(VLOOKUP(A124,Employee_Master!A:B,2,0),"")</f>
-        <v>Partap</v>
+        <v>Risha Bansal</v>
       </c>
       <c r="C124" s="7" t="str">
         <f>IFERROR(VLOOKUP(A124,Employee_Master!A:B,3,0),"")</f>
@@ -41268,50 +41276,50 @@
       </c>
       <c r="D124" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A124,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A124,Participation_Entry!L:L))</f>
-        <v>40.225200000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="6">
-        <v>467544</v>
+        <v>459234</v>
       </c>
       <c r="B125" s="7" t="str">
         <f>IFERROR(VLOOKUP(A125,Employee_Master!A:B,2,0),"")</f>
-        <v>Vinay Kumar</v>
+        <v>Ritik Kumar</v>
       </c>
       <c r="C125" s="7" t="str">
         <f>IFERROR(VLOOKUP(A125,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D125" s="7">
+      <c r="D125" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A125,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A125,Participation_Entry!L:L))</f>
-        <v>92.006399999999999</v>
+        <v/>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="6">
-        <v>474194</v>
+        <v>467075</v>
       </c>
       <c r="B126" s="7" t="str">
         <f>IFERROR(VLOOKUP(A126,Employee_Master!A:B,2,0),"")</f>
-        <v>Rohit Yadav</v>
+        <v>Ritish</v>
       </c>
       <c r="C126" s="7" t="str">
         <f>IFERROR(VLOOKUP(A126,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D126" s="7">
+      <c r="D126" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A126,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A126,Participation_Entry!L:L))</f>
-        <v>134.0658</v>
+        <v/>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="6">
-        <v>472840</v>
+        <v>452118</v>
       </c>
       <c r="B127" s="7" t="str">
         <f>IFERROR(VLOOKUP(A127,Employee_Master!A:B,2,0),"")</f>
-        <v>Supravat Adhikary</v>
+        <v>Riya Kumari</v>
       </c>
       <c r="C127" s="7" t="str">
         <f>IFERROR(VLOOKUP(A127,Employee_Master!A:B,3,0),"")</f>
@@ -41319,16 +41327,16 @@
       </c>
       <c r="D127" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A127,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A127,Participation_Entry!L:L))</f>
-        <v>60.308099999999996</v>
+        <v>59.468599999999995</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="6">
-        <v>476372</v>
+        <v>427154</v>
       </c>
       <c r="B128" s="7" t="str">
         <f>IFERROR(VLOOKUP(A128,Employee_Master!A:B,2,0),"")</f>
-        <v>Laksh</v>
+        <v>Rohan Mehra</v>
       </c>
       <c r="C128" s="7" t="str">
         <f>IFERROR(VLOOKUP(A128,Employee_Master!A:B,3,0),"")</f>
@@ -41336,16 +41344,16 @@
       </c>
       <c r="D128" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A128,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A128,Participation_Entry!L:L))</f>
-        <v>74.443899999999999</v>
+        <v>45.870600000000003</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="6">
-        <v>478084</v>
+        <v>463660</v>
       </c>
       <c r="B129" s="7" t="str">
         <f>IFERROR(VLOOKUP(A129,Employee_Master!A:B,2,0),"")</f>
-        <v>Ashish Mishra</v>
+        <v>Rohit Sharma</v>
       </c>
       <c r="C129" s="7" t="str">
         <f>IFERROR(VLOOKUP(A129,Employee_Master!A:B,3,0),"")</f>
@@ -41353,16 +41361,16 @@
       </c>
       <c r="D129" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A129,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A129,Participation_Entry!L:L))</f>
-        <v>102.2955</v>
+        <v>26.242999999999999</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="6">
-        <v>453948</v>
+        <v>474194</v>
       </c>
       <c r="B130" s="7" t="str">
         <f>IFERROR(VLOOKUP(A130,Employee_Master!A:B,2,0),"")</f>
-        <v>Ashish Bhardwaj</v>
+        <v>Rohit Yadav</v>
       </c>
       <c r="C130" s="7" t="str">
         <f>IFERROR(VLOOKUP(A130,Employee_Master!A:B,3,0),"")</f>
@@ -41370,16 +41378,16 @@
       </c>
       <c r="D130" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A130,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A130,Participation_Entry!L:L))</f>
-        <v>68.705600000000004</v>
+        <v>134.0658</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="6">
-        <v>460692</v>
+        <v>452056</v>
       </c>
       <c r="B131" s="7" t="str">
         <f>IFERROR(VLOOKUP(A131,Employee_Master!A:B,2,0),"")</f>
-        <v>Mayank Arya</v>
+        <v xml:space="preserve">Rupesh </v>
       </c>
       <c r="C131" s="7" t="str">
         <f>IFERROR(VLOOKUP(A131,Employee_Master!A:B,3,0),"")</f>
@@ -41387,16 +41395,16 @@
       </c>
       <c r="D131" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A131,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A131,Participation_Entry!L:L))</f>
-        <v>74.301100000000005</v>
+        <v>105.39600000000002</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="6">
-        <v>435877</v>
+        <v>432865</v>
       </c>
       <c r="B132" s="7" t="str">
         <f>IFERROR(VLOOKUP(A132,Employee_Master!A:B,2,0),"")</f>
-        <v>Pardeep Kumar</v>
+        <v>Rupesh Gandhi</v>
       </c>
       <c r="C132" s="7" t="str">
         <f>IFERROR(VLOOKUP(A132,Employee_Master!A:B,3,0),"")</f>
@@ -41404,16 +41412,16 @@
       </c>
       <c r="D132" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A132,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A132,Participation_Entry!L:L))</f>
-        <v>19.581299999999999</v>
+        <v>70.215699999999998</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="6">
-        <v>440620</v>
+        <v>457157</v>
       </c>
       <c r="B133" s="7" t="str">
         <f>IFERROR(VLOOKUP(A133,Employee_Master!A:B,2,0),"")</f>
-        <v>Kuldeep Singh</v>
+        <v>Sachin Kashyap</v>
       </c>
       <c r="C133" s="7" t="str">
         <f>IFERROR(VLOOKUP(A133,Employee_Master!A:B,3,0),"")</f>
@@ -41421,33 +41429,33 @@
       </c>
       <c r="D133" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A133,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A133,Participation_Entry!L:L))</f>
-        <v>83.278599999999997</v>
+        <v>182.5196</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="6">
-        <v>449551</v>
+        <v>450693</v>
       </c>
       <c r="B134" s="7" t="str">
         <f>IFERROR(VLOOKUP(A134,Employee_Master!A:B,2,0),"")</f>
-        <v>Ramesh Kumar</v>
+        <v>Sagar rana</v>
       </c>
       <c r="C134" s="7" t="str">
         <f>IFERROR(VLOOKUP(A134,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D134" s="7">
+      <c r="D134" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A134,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A134,Participation_Entry!L:L))</f>
-        <v>30</v>
+        <v/>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="6">
-        <v>452799</v>
+        <v>452057</v>
       </c>
       <c r="B135" s="7" t="str">
         <f>IFERROR(VLOOKUP(A135,Employee_Master!A:B,2,0),"")</f>
-        <v>Manish Kukreti</v>
+        <v xml:space="preserve">Sahil Thakur </v>
       </c>
       <c r="C135" s="7" t="str">
         <f>IFERROR(VLOOKUP(A135,Employee_Master!A:B,3,0),"")</f>
@@ -41455,16 +41463,16 @@
       </c>
       <c r="D135" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A135,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A135,Participation_Entry!L:L))</f>
-        <v>111.68900000000001</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="6">
-        <v>438864</v>
+        <v>705995</v>
       </c>
       <c r="B136" s="7" t="str">
         <f>IFERROR(VLOOKUP(A136,Employee_Master!A:B,2,0),"")</f>
-        <v>Rajan Gupta</v>
+        <v>Sahil.</v>
       </c>
       <c r="C136" s="7" t="str">
         <f>IFERROR(VLOOKUP(A136,Employee_Master!A:B,3,0),"")</f>
@@ -41472,16 +41480,16 @@
       </c>
       <c r="D136" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A136,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A136,Participation_Entry!L:L))</f>
-        <v>53.038200000000003</v>
+        <v>58.816200000000009</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="6">
-        <v>463059</v>
+        <v>468660</v>
       </c>
       <c r="B137" s="7" t="str">
         <f>IFERROR(VLOOKUP(A137,Employee_Master!A:B,2,0),"")</f>
-        <v>Parvinder</v>
+        <v>Samay Raj</v>
       </c>
       <c r="C137" s="7" t="str">
         <f>IFERROR(VLOOKUP(A137,Employee_Master!A:B,3,0),"")</f>
@@ -41489,16 +41497,16 @@
       </c>
       <c r="D137" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A137,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A137,Participation_Entry!L:L))</f>
-        <v>71.264399999999995</v>
+        <v>115.3021</v>
       </c>
     </row>
     <row r="138" spans="1:4">
-      <c r="A138" s="6">
-        <v>455024</v>
+      <c r="A138" s="15">
+        <v>412273</v>
       </c>
       <c r="B138" s="7" t="str">
         <f>IFERROR(VLOOKUP(A138,Employee_Master!A:B,2,0),"")</f>
-        <v>Dileep Kumar</v>
+        <v>Sandeep Sengar</v>
       </c>
       <c r="C138" s="7" t="str">
         <f>IFERROR(VLOOKUP(A138,Employee_Master!A:B,3,0),"")</f>
@@ -41506,33 +41514,33 @@
       </c>
       <c r="D138" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A138,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A138,Participation_Entry!L:L))</f>
-        <v>31.736699999999999</v>
+        <v>21.326900000000002</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="6">
-        <v>449891</v>
+        <v>407302</v>
       </c>
       <c r="B139" s="7" t="str">
         <f>IFERROR(VLOOKUP(A139,Employee_Master!A:B,2,0),"")</f>
-        <v>Komalpreet</v>
+        <v>Sanjaya Sahoo</v>
       </c>
       <c r="C139" s="7" t="str">
         <f>IFERROR(VLOOKUP(A139,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D139" s="7">
+      <c r="D139" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A139,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A139,Participation_Entry!L:L))</f>
-        <v>119.6532</v>
+        <v/>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="6">
-        <v>450224</v>
+        <v>472322</v>
       </c>
       <c r="B140" s="7" t="str">
         <f>IFERROR(VLOOKUP(A140,Employee_Master!A:B,2,0),"")</f>
-        <v>Lalit Nagar</v>
+        <v>Sanjeet Kumar</v>
       </c>
       <c r="C140" s="7" t="str">
         <f>IFERROR(VLOOKUP(A140,Employee_Master!A:B,3,0),"")</f>
@@ -41540,16 +41548,16 @@
       </c>
       <c r="D140" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A140,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A140,Participation_Entry!L:L))</f>
-        <v>29.381999999999998</v>
+        <v>68.516800000000003</v>
       </c>
     </row>
     <row r="141" spans="1:4">
-      <c r="A141" s="6">
-        <v>450171</v>
+      <c r="A141" s="15">
+        <v>438679</v>
       </c>
       <c r="B141" s="7" t="str">
         <f>IFERROR(VLOOKUP(A141,Employee_Master!A:B,2,0),"")</f>
-        <v>Manpreet Kaur</v>
+        <v>Saurabh Kumar</v>
       </c>
       <c r="C141" s="7" t="str">
         <f>IFERROR(VLOOKUP(A141,Employee_Master!A:B,3,0),"")</f>
@@ -41557,16 +41565,16 @@
       </c>
       <c r="D141" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A141,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A141,Participation_Entry!L:L))</f>
-        <v>69.037800000000004</v>
+        <v>75.917199999999994</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="6">
-        <v>450230</v>
+        <v>478269</v>
       </c>
       <c r="B142" s="7" t="str">
         <f>IFERROR(VLOOKUP(A142,Employee_Master!A:B,2,0),"")</f>
-        <v>Aarti Gupta</v>
+        <v xml:space="preserve">Saurabh kumar </v>
       </c>
       <c r="C142" s="7" t="str">
         <f>IFERROR(VLOOKUP(A142,Employee_Master!A:B,3,0),"")</f>
@@ -41574,16 +41582,16 @@
       </c>
       <c r="D142" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A142,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A142,Participation_Entry!L:L))</f>
-        <v>72.238799999999998</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="6">
-        <v>452059</v>
+        <v>700216</v>
       </c>
       <c r="B143" s="7" t="str">
         <f>IFERROR(VLOOKUP(A143,Employee_Master!A:B,2,0),"")</f>
-        <v>Mahi Singh</v>
+        <v>Shivam Rani</v>
       </c>
       <c r="C143" s="7" t="str">
         <f>IFERROR(VLOOKUP(A143,Employee_Master!A:B,3,0),"")</f>
@@ -41591,16 +41599,16 @@
       </c>
       <c r="D143" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A143,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A143,Participation_Entry!L:L))</f>
-        <v>38.909199999999998</v>
+        <v>43.619</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="6">
-        <v>466167</v>
+        <v>452076</v>
       </c>
       <c r="B144" s="7" t="str">
         <f>IFERROR(VLOOKUP(A144,Employee_Master!A:B,2,0),"")</f>
-        <v>Aishwarya Sharma</v>
+        <v>Shraddha Singh</v>
       </c>
       <c r="C144" s="7" t="str">
         <f>IFERROR(VLOOKUP(A144,Employee_Master!A:B,3,0),"")</f>
@@ -41608,16 +41616,16 @@
       </c>
       <c r="D144" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A144,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A144,Participation_Entry!L:L))</f>
-        <v>151.4357</v>
+        <v>80.214100000000002</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="6">
-        <v>452076</v>
+        <v>450228</v>
       </c>
       <c r="B145" s="7" t="str">
         <f>IFERROR(VLOOKUP(A145,Employee_Master!A:B,2,0),"")</f>
-        <v>Shraddha Singh</v>
+        <v>Shubham Sharma</v>
       </c>
       <c r="C145" s="7" t="str">
         <f>IFERROR(VLOOKUP(A145,Employee_Master!A:B,3,0),"")</f>
@@ -41625,16 +41633,16 @@
       </c>
       <c r="D145" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A145,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A145,Participation_Entry!L:L))</f>
-        <v>80.214100000000002</v>
+        <v>69.331400000000002</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="6">
-        <v>468887</v>
+        <v>708792</v>
       </c>
       <c r="B146" s="7" t="str">
         <f>IFERROR(VLOOKUP(A146,Employee_Master!A:B,2,0),"")</f>
-        <v>Prachi Shukla</v>
+        <v>Shubhanshu Pandey</v>
       </c>
       <c r="C146" s="7" t="str">
         <f>IFERROR(VLOOKUP(A146,Employee_Master!A:B,3,0),"")</f>
@@ -41642,16 +41650,16 @@
       </c>
       <c r="D146" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A146,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A146,Participation_Entry!L:L))</f>
-        <v>23.021100000000001</v>
+        <v>43.544800000000002</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="6">
-        <v>470301</v>
+        <v>446300</v>
       </c>
       <c r="B147" s="7" t="str">
         <f>IFERROR(VLOOKUP(A147,Employee_Master!A:B,2,0),"")</f>
-        <v>Ankit Kumar</v>
+        <v>Simranjit Singh</v>
       </c>
       <c r="C147" s="7" t="str">
         <f>IFERROR(VLOOKUP(A147,Employee_Master!A:B,3,0),"")</f>
@@ -41659,33 +41667,33 @@
       </c>
       <c r="D147" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A147,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A147,Participation_Entry!L:L))</f>
-        <v>76.212099999999992</v>
+        <v>80.99799999999999</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="6">
-        <v>471387</v>
+        <v>450325</v>
       </c>
       <c r="B148" s="7" t="str">
         <f>IFERROR(VLOOKUP(A148,Employee_Master!A:B,2,0),"")</f>
-        <v>Neeraj</v>
+        <v>Simratpal Singh</v>
       </c>
       <c r="C148" s="7" t="str">
         <f>IFERROR(VLOOKUP(A148,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D148" s="7">
+      <c r="D148" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A148,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A148,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v/>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="6">
-        <v>478269</v>
+        <v>720995</v>
       </c>
       <c r="B149" s="7" t="str">
         <f>IFERROR(VLOOKUP(A149,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Saurabh kumar </v>
+        <v>Sinjan Bhar</v>
       </c>
       <c r="C149" s="7" t="str">
         <f>IFERROR(VLOOKUP(A149,Employee_Master!A:B,3,0),"")</f>
@@ -41698,11 +41706,11 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="6">
-        <v>478266</v>
+        <v>469617</v>
       </c>
       <c r="B150" s="7" t="str">
         <f>IFERROR(VLOOKUP(A150,Employee_Master!A:B,2,0),"")</f>
-        <v xml:space="preserve">Abhishek Sharma </v>
+        <v>Siyaram</v>
       </c>
       <c r="C150" s="7" t="str">
         <f>IFERROR(VLOOKUP(A150,Employee_Master!A:B,3,0),"")</f>
@@ -41710,16 +41718,16 @@
       </c>
       <c r="D150" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A150,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A150,Participation_Entry!L:L))</f>
-        <v>35.4343</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="6">
-        <v>427154</v>
+        <v>460628</v>
       </c>
       <c r="B151" s="7" t="str">
         <f>IFERROR(VLOOKUP(A151,Employee_Master!A:B,2,0),"")</f>
-        <v>Rohan Mehra</v>
+        <v>Smarth</v>
       </c>
       <c r="C151" s="7" t="str">
         <f>IFERROR(VLOOKUP(A151,Employee_Master!A:B,3,0),"")</f>
@@ -41727,16 +41735,16 @@
       </c>
       <c r="D151" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A151,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A151,Participation_Entry!L:L))</f>
-        <v>45.870600000000003</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="6">
-        <v>700216</v>
+        <v>721765</v>
       </c>
       <c r="B152" s="7" t="str">
         <f>IFERROR(VLOOKUP(A152,Employee_Master!A:B,2,0),"")</f>
-        <v>Shivam Rani</v>
+        <v>Sneha .</v>
       </c>
       <c r="C152" s="7" t="str">
         <f>IFERROR(VLOOKUP(A152,Employee_Master!A:B,3,0),"")</f>
@@ -41744,16 +41752,16 @@
       </c>
       <c r="D152" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A152,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A152,Participation_Entry!L:L))</f>
-        <v>43.619</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="6">
-        <v>705995</v>
+        <v>452074</v>
       </c>
       <c r="B153" s="7" t="str">
         <f>IFERROR(VLOOKUP(A153,Employee_Master!A:B,2,0),"")</f>
-        <v>Sahil.</v>
+        <v>Sneha Singh</v>
       </c>
       <c r="C153" s="7" t="str">
         <f>IFERROR(VLOOKUP(A153,Employee_Master!A:B,3,0),"")</f>
@@ -41761,11 +41769,11 @@
       </c>
       <c r="D153" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A153,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A153,Participation_Entry!L:L))</f>
-        <v>58.816200000000009</v>
+        <v>36.646599999999999</v>
       </c>
     </row>
     <row r="154" spans="1:4">
-      <c r="A154" s="6">
+      <c r="A154" s="15">
         <v>706181</v>
       </c>
       <c r="B154" s="7" t="str">
@@ -41799,29 +41807,29 @@
       </c>
     </row>
     <row r="156" spans="1:4">
-      <c r="A156" s="6">
-        <v>705909</v>
+      <c r="A156" s="15">
+        <v>479827</v>
       </c>
       <c r="B156" s="7" t="str">
         <f>IFERROR(VLOOKUP(A156,Employee_Master!A:B,2,0),"")</f>
-        <v>Tanmay Ghosal</v>
+        <v>Sunil Kr. Singh</v>
       </c>
       <c r="C156" s="7" t="str">
         <f>IFERROR(VLOOKUP(A156,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D156" s="7" t="str">
+      <c r="D156" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A156,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A156,Participation_Entry!L:L))</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="6">
-        <v>707131</v>
+        <v>472840</v>
       </c>
       <c r="B157" s="7" t="str">
         <f>IFERROR(VLOOKUP(A157,Employee_Master!A:B,2,0),"")</f>
-        <v>Puja Bhalotia</v>
+        <v>Supravat Adhikary</v>
       </c>
       <c r="C157" s="7" t="str">
         <f>IFERROR(VLOOKUP(A157,Employee_Master!A:B,3,0),"")</f>
@@ -41829,33 +41837,33 @@
       </c>
       <c r="D157" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A157,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A157,Participation_Entry!L:L))</f>
-        <v>53.310899999999997</v>
+        <v>60.308099999999996</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="6">
-        <v>708792</v>
+        <v>460627</v>
       </c>
       <c r="B158" s="7" t="str">
         <f>IFERROR(VLOOKUP(A158,Employee_Master!A:B,2,0),"")</f>
-        <v>Shubhanshu Pandey</v>
+        <v>Sushil</v>
       </c>
       <c r="C158" s="7" t="str">
         <f>IFERROR(VLOOKUP(A158,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D158" s="7">
+      <c r="D158" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A158,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A158,Participation_Entry!L:L))</f>
-        <v>43.544800000000002</v>
+        <v/>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="6">
-        <v>709664</v>
+        <v>449635</v>
       </c>
       <c r="B159" s="7" t="str">
         <f>IFERROR(VLOOKUP(A159,Employee_Master!A:B,2,0),"")</f>
-        <v>Kavita Rathore</v>
+        <v>Sushma Tiwari</v>
       </c>
       <c r="C159" s="7" t="str">
         <f>IFERROR(VLOOKUP(A159,Employee_Master!A:B,3,0),"")</f>
@@ -41863,33 +41871,33 @@
       </c>
       <c r="D159" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A159,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A159,Participation_Entry!L:L))</f>
-        <v>55.380699999999997</v>
+        <v>68.346299999999999</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="6">
-        <v>710013</v>
+        <v>705909</v>
       </c>
       <c r="B160" s="7" t="str">
         <f>IFERROR(VLOOKUP(A160,Employee_Master!A:B,2,0),"")</f>
-        <v>Jyoti Saini</v>
+        <v>Tanmay Ghosal</v>
       </c>
       <c r="C160" s="7" t="str">
         <f>IFERROR(VLOOKUP(A160,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D160" s="7">
+      <c r="D160" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A160,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A160,Participation_Entry!L:L))</f>
-        <v>66.440899999999999</v>
+        <v/>
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="6">
-        <v>710555</v>
+      <c r="A161" s="15">
+        <v>423859</v>
       </c>
       <c r="B161" s="7" t="str">
         <f>IFERROR(VLOOKUP(A161,Employee_Master!A:B,2,0),"")</f>
-        <v>Jyoti Chauhan</v>
+        <v>Tilak Raj</v>
       </c>
       <c r="C161" s="7" t="str">
         <f>IFERROR(VLOOKUP(A161,Employee_Master!A:B,3,0),"")</f>
@@ -41901,12 +41909,12 @@
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="6">
-        <v>426232</v>
+      <c r="A162" s="15">
+        <v>450437</v>
       </c>
       <c r="B162" s="7" t="str">
         <f>IFERROR(VLOOKUP(A162,Employee_Master!A:B,2,0),"")</f>
-        <v>Varish Hussain</v>
+        <v xml:space="preserve">Tinku Shekhawat </v>
       </c>
       <c r="C162" s="7" t="str">
         <f>IFERROR(VLOOKUP(A162,Employee_Master!A:B,3,0),"")</f>
@@ -41914,16 +41922,16 @@
       </c>
       <c r="D162" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A162,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A162,Participation_Entry!L:L))</f>
-        <v>59.432099999999991</v>
+        <v>47.703400000000002</v>
       </c>
     </row>
     <row r="163" spans="1:4">
-      <c r="A163" s="6">
-        <v>712428</v>
+      <c r="A163" s="15">
+        <v>426232</v>
       </c>
       <c r="B163" s="7" t="str">
         <f>IFERROR(VLOOKUP(A163,Employee_Master!A:B,2,0),"")</f>
-        <v>Akanksha Gangwar</v>
+        <v>Varish Hussain</v>
       </c>
       <c r="C163" s="7" t="str">
         <f>IFERROR(VLOOKUP(A163,Employee_Master!A:B,3,0),"")</f>
@@ -41931,33 +41939,33 @@
       </c>
       <c r="D163" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A163,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A163,Participation_Entry!L:L))</f>
-        <v>73.302199999999999</v>
+        <v>59.432099999999991</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="6">
-        <v>435548</v>
+        <v>466562</v>
       </c>
       <c r="B164" s="7" t="str">
         <f>IFERROR(VLOOKUP(A164,Employee_Master!A:B,2,0),"")</f>
-        <v>Gurwant Sran</v>
+        <v>Vikas Bhardwaj</v>
       </c>
       <c r="C164" s="7" t="str">
         <f>IFERROR(VLOOKUP(A164,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D164" s="7">
+      <c r="D164" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A164,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A164,Participation_Entry!L:L))</f>
-        <v>67.009199999999993</v>
+        <v/>
       </c>
     </row>
     <row r="165" spans="1:4">
-      <c r="A165" s="6">
-        <v>716610</v>
+      <c r="A165" s="15">
+        <v>438263</v>
       </c>
       <c r="B165" s="7" t="str">
         <f>IFERROR(VLOOKUP(A165,Employee_Master!A:B,2,0),"")</f>
-        <v>Naval Singh</v>
+        <v>Vikash Kumar</v>
       </c>
       <c r="C165" s="7" t="str">
         <f>IFERROR(VLOOKUP(A165,Employee_Master!A:B,3,0),"")</f>
@@ -41965,16 +41973,16 @@
       </c>
       <c r="D165" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A165,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A165,Participation_Entry!L:L))</f>
-        <v>108.3938</v>
+        <v>63.443200000000004</v>
       </c>
     </row>
     <row r="166" spans="1:4">
-      <c r="A166" s="6">
-        <v>720995</v>
+      <c r="A166" s="15">
+        <v>467544</v>
       </c>
       <c r="B166" s="7" t="str">
         <f>IFERROR(VLOOKUP(A166,Employee_Master!A:B,2,0),"")</f>
-        <v>Sinjan Bhar</v>
+        <v>Vinay Kumar</v>
       </c>
       <c r="C166" s="7" t="str">
         <f>IFERROR(VLOOKUP(A166,Employee_Master!A:B,3,0),"")</f>
@@ -41982,50 +41990,50 @@
       </c>
       <c r="D166" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A166,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A166,Participation_Entry!L:L))</f>
-        <v>10</v>
+        <v>92.006399999999999</v>
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="6">
-        <v>721766</v>
+      <c r="A167" s="15">
+        <v>468536</v>
       </c>
       <c r="B167" s="7" t="str">
         <f>IFERROR(VLOOKUP(A167,Employee_Master!A:B,2,0),"")</f>
-        <v>BHAWNA SHARMA</v>
+        <v>Vinod Kumar</v>
       </c>
       <c r="C167" s="7" t="str">
         <f>IFERROR(VLOOKUP(A167,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D167" s="7">
+      <c r="D167" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A167,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A167,Participation_Entry!L:L))</f>
-        <v>20</v>
+        <v/>
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="6">
-        <v>721765</v>
+      <c r="A168" s="15">
+        <v>470292</v>
       </c>
       <c r="B168" s="7" t="str">
         <f>IFERROR(VLOOKUP(A168,Employee_Master!A:B,2,0),"")</f>
-        <v>Sneha .</v>
+        <v>Vishal Kumar</v>
       </c>
       <c r="C168" s="7" t="str">
         <f>IFERROR(VLOOKUP(A168,Employee_Master!A:B,3,0),"")</f>
         <v/>
       </c>
-      <c r="D168" s="7">
+      <c r="D168" s="7" t="str">
         <f>IF(SUMIF(Participation_Entry!B:B,A168,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A168,Participation_Entry!L:L))</f>
-        <v>30</v>
+        <v/>
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="6">
-        <v>721899</v>
+      <c r="A169" s="15">
+        <v>451509</v>
       </c>
       <c r="B169" s="7" t="str">
         <f>IFERROR(VLOOKUP(A169,Employee_Master!A:B,2,0),"")</f>
-        <v>Khushboo Yadav</v>
+        <v>Vivek Aswal</v>
       </c>
       <c r="C169" s="7" t="str">
         <f>IFERROR(VLOOKUP(A169,Employee_Master!A:B,3,0),"")</f>
@@ -42033,16 +42041,16 @@
       </c>
       <c r="D169" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A169,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A169,Participation_Entry!L:L))</f>
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="6">
-        <v>722356</v>
+      <c r="A170" s="15">
+        <v>451609</v>
       </c>
       <c r="B170" s="7" t="str">
         <f>IFERROR(VLOOKUP(A170,Employee_Master!A:B,2,0),"")</f>
-        <v>Ashita Munjley</v>
+        <v>Vivek Kumar Yadav</v>
       </c>
       <c r="C170" s="7" t="str">
         <f>IFERROR(VLOOKUP(A170,Employee_Master!A:B,3,0),"")</f>
@@ -42050,16 +42058,16 @@
       </c>
       <c r="D170" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A170,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A170,Participation_Entry!L:L))</f>
-        <v>34.984099999999998</v>
+        <v>92.552499999999995</v>
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="6">
-        <v>722393</v>
+      <c r="A171" s="15">
+        <v>467519</v>
       </c>
       <c r="B171" s="7" t="str">
         <f>IFERROR(VLOOKUP(A171,Employee_Master!A:B,2,0),"")</f>
-        <v>Koteswara Devireddy</v>
+        <v>Vivek Tiwari</v>
       </c>
       <c r="C171" s="7" t="str">
         <f>IFERROR(VLOOKUP(A171,Employee_Master!A:B,3,0),"")</f>
@@ -42067,12 +42075,202 @@
       </c>
       <c r="D171" s="7">
         <f>IF(SUMIF(Participation_Entry!B:B,A171,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A171,Participation_Entry!L:L))</f>
-        <v>113.37639999999999</v>
+        <v>62.805900000000001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="15">
+        <v>460888</v>
+      </c>
+      <c r="B172" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A172,Employee_Master!A:B,2,0),"")</f>
+        <v>Yatin</v>
+      </c>
+      <c r="C172" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A172,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D172" s="7" t="str">
+        <f>IF(SUMIF(Participation_Entry!B:B,A172,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A172,Participation_Entry!L:L))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="15">
+        <v>722751</v>
+      </c>
+      <c r="B173" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A173,Employee_Master!A:B,2,0),"")</f>
+        <v>Palak</v>
+      </c>
+      <c r="C173" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A173,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D173" s="7">
+        <f>IF(SUMIF(Participation_Entry!B:B,A173,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A173,Participation_Entry!L:L))</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="15">
+        <v>722783</v>
+      </c>
+      <c r="B174" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A174,Employee_Master!A:B,2,0),"")</f>
+        <v>Anjali</v>
+      </c>
+      <c r="C174" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A174,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D174" s="7">
+        <f>IF(SUMIF(Participation_Entry!B:B,A174,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A174,Participation_Entry!L:L))</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="15">
+        <v>723888</v>
+      </c>
+      <c r="B175" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A175,Employee_Master!A:B,2,0),"")</f>
+        <v>Deepak Tiwari</v>
+      </c>
+      <c r="C175" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A175,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D175" s="7">
+        <f>IF(SUMIF(Participation_Entry!B:B,A175,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A175,Participation_Entry!L:L))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="15">
+        <v>722752</v>
+      </c>
+      <c r="B176" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A176,Employee_Master!A:B,2,0),"")</f>
+        <v>Monika Jain</v>
+      </c>
+      <c r="C176" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A176,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D176" s="7">
+        <f>IF(SUMIF(Participation_Entry!B:B,A176,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A176,Participation_Entry!L:L))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="15">
+        <v>725073</v>
+      </c>
+      <c r="B177" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A177,Employee_Master!A:B,2,0),"")</f>
+        <v>Pinki Gupta</v>
+      </c>
+      <c r="C177" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A177,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D177" s="7">
+        <f>IF(SUMIF(Participation_Entry!B:B,A177,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A177,Participation_Entry!L:L))</f>
+        <v>26.9648</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="15">
+        <v>722782</v>
+      </c>
+      <c r="B178" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A178,Employee_Master!A:B,2,0),"")</f>
+        <v>Kriti</v>
+      </c>
+      <c r="C178" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A178,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D178" s="7">
+        <f>IF(SUMIF(Participation_Entry!B:B,A178,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A178,Participation_Entry!L:L))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="15">
+        <v>724729</v>
+      </c>
+      <c r="B179" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A179,Employee_Master!A:B,2,0),"")</f>
+        <v>Akash Kumar</v>
+      </c>
+      <c r="C179" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A179,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D179" s="7" t="str">
+        <f>IF(SUMIF(Participation_Entry!B:B,A179,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A179,Participation_Entry!L:L))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="15">
+        <v>725373</v>
+      </c>
+      <c r="B180" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A180,Employee_Master!A:B,2,0),"")</f>
+        <v>Ishan Kalia</v>
+      </c>
+      <c r="C180" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A180,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D180" s="7" t="str">
+        <f>IF(SUMIF(Participation_Entry!B:B,A180,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A180,Participation_Entry!L:L))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="15">
+        <v>726234</v>
+      </c>
+      <c r="B181" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A181,Employee_Master!A:B,2,0),"")</f>
+        <v>Jaspal Singh</v>
+      </c>
+      <c r="C181" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A181,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D181" s="7" t="str">
+        <f>IF(SUMIF(Participation_Entry!B:B,A181,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A181,Participation_Entry!L:L))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="15">
+        <v>726299</v>
+      </c>
+      <c r="B182" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A182,Employee_Master!A:B,2,0),"")</f>
+        <v>Anu Devi</v>
+      </c>
+      <c r="C182" s="7" t="str">
+        <f>IFERROR(VLOOKUP(A182,Employee_Master!A:B,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="D182" s="7" t="str">
+        <f>IF(SUMIF(Participation_Entry!B:B,A182,Participation_Entry!L:L)=0,"",SUMIF(Participation_Entry!B:B,A182,Participation_Entry!L:L))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="top10" dxfId="0" priority="1" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="1" priority="2" percent="1" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A182">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
